--- a/data/constraints_sector_model.xlsx
+++ b/data/constraints_sector_model.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schneids\code\building-archetype-inference\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56BB07B-EC24-4E49-B29E-C9A9649F05B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB88BC0B-F37E-40B8-BA7F-20C724F019F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="-17484" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{675A66AE-0C9B-47B8-A3BC-119353CCB9E0}"/>
+    <workbookView xWindow="-18060" yWindow="-17388" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{675A66AE-0C9B-47B8-A3BC-119353CCB9E0}"/>
   </bookViews>
   <sheets>
     <sheet name="constraints" sheetId="1" r:id="rId1"/>
     <sheet name="NGF" sheetId="2" r:id="rId2"/>
+    <sheet name="ENDEnergie" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="72">
   <si>
     <t>building_specific_value</t>
   </si>
@@ -247,6 +248,15 @@
   </si>
   <si>
     <t>Wien</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Gas XY</t>
   </si>
 </sst>
 </file>
@@ -774,20 +784,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825ECA7B-4D54-4BD7-83FF-11EABBB95258}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" customWidth="1"/>
-    <col min="4" max="4" width="76.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="4" max="4" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -839,7 +849,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -861,7 +871,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -883,7 +893,7 @@
       <c r="J4" s="8"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -905,7 +915,7 @@
       <c r="J5" s="8"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -927,7 +937,7 @@
       <c r="J6" s="8"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -947,7 +957,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -967,7 +977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -987,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1007,7 +1017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1027,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1047,7 +1057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1067,7 +1077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="11:11" x14ac:dyDescent="0.35">
       <c r="K27" s="9"/>
     </row>
   </sheetData>
@@ -1085,15 +1095,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF107C16-0C2C-4DE3-BA55-525B5CFB1389}">
   <dimension ref="A1:G901"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="7" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>36</v>
       </c>
@@ -1116,7 +1126,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="13">
         <v>2021</v>
       </c>
@@ -1139,7 +1149,7 @@
         <v>983229</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16">
         <v>2021</v>
       </c>
@@ -1162,7 +1172,7 @@
         <v>391933</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="13">
         <v>2021</v>
       </c>
@@ -1185,7 +1195,7 @@
         <v>594234</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16">
         <v>2021</v>
       </c>
@@ -1208,7 +1218,7 @@
         <v>629490</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="13">
         <v>2021</v>
       </c>
@@ -1231,7 +1241,7 @@
         <v>634503</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>2021</v>
       </c>
@@ -1254,7 +1264,7 @@
         <v>653133</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
         <v>2021</v>
       </c>
@@ -1277,7 +1287,7 @@
         <v>573485</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16">
         <v>2021</v>
       </c>
@@ -1300,7 +1310,7 @@
         <v>603461</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
         <v>2021</v>
       </c>
@@ -1323,7 +1333,7 @@
         <v>610016</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16">
         <v>2021</v>
       </c>
@@ -1346,7 +1356,7 @@
         <v>1223343</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>2021</v>
       </c>
@@ -1369,7 +1379,7 @@
         <v>488932</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16">
         <v>2021</v>
       </c>
@@ -1392,7 +1402,7 @@
         <v>742492</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>2021</v>
       </c>
@@ -1415,7 +1425,7 @@
         <v>817702</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16">
         <v>2021</v>
       </c>
@@ -1438,7 +1448,7 @@
         <v>844220</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
         <v>2021</v>
       </c>
@@ -1461,7 +1471,7 @@
         <v>792641</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="16">
         <v>2021</v>
       </c>
@@ -1484,7 +1494,7 @@
         <v>671625</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
         <v>2021</v>
       </c>
@@ -1507,7 +1517,7 @@
         <v>693748</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16">
         <v>2021</v>
       </c>
@@ -1530,7 +1540,7 @@
         <v>501465</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>2021</v>
       </c>
@@ -1553,7 +1563,7 @@
         <v>3721405</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16">
         <v>2021</v>
       </c>
@@ -1576,7 +1586,7 @@
         <v>1272798</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
         <v>2021</v>
       </c>
@@ -1599,7 +1609,7 @@
         <v>2037561</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="16">
         <v>2021</v>
       </c>
@@ -1622,7 +1632,7 @@
         <v>2460003</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
         <v>2021</v>
       </c>
@@ -1645,7 +1655,7 @@
         <v>2771785</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>2021</v>
       </c>
@@ -1668,7 +1678,7 @@
         <v>2664620</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
         <v>2021</v>
       </c>
@@ -1691,7 +1701,7 @@
         <v>2272329</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="16">
         <v>2021</v>
       </c>
@@ -1714,7 +1724,7 @@
         <v>2344643</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
         <v>2021</v>
       </c>
@@ -1737,7 +1747,7 @@
         <v>1379254</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="16">
         <v>2021</v>
       </c>
@@ -1760,7 +1770,7 @@
         <v>8955447</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>2021</v>
       </c>
@@ -1783,7 +1793,7 @@
         <v>2646843</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="16">
         <v>2021</v>
       </c>
@@ -1806,7 +1816,7 @@
         <v>4421437</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>2021</v>
       </c>
@@ -1829,7 +1839,7 @@
         <v>5724828</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="16">
         <v>2021</v>
       </c>
@@ -1852,7 +1862,7 @@
         <v>6967076</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
         <v>2021</v>
       </c>
@@ -1875,7 +1885,7 @@
         <v>6503192</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>2021</v>
       </c>
@@ -1898,7 +1908,7 @@
         <v>5148653</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
         <v>2021</v>
       </c>
@@ -1921,7 +1931,7 @@
         <v>5808565</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="16">
         <v>2021</v>
       </c>
@@ -1944,7 +1954,7 @@
         <v>3386606</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
         <v>2021</v>
       </c>
@@ -1967,7 +1977,7 @@
         <v>37971840</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="16">
         <v>2021</v>
       </c>
@@ -1990,7 +2000,7 @@
         <v>10637160</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="13">
         <v>2021</v>
       </c>
@@ -2013,7 +2023,7 @@
         <v>16161055</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="16">
         <v>2021</v>
       </c>
@@ -2036,7 +2046,7 @@
         <v>25661130</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="13">
         <v>2021</v>
       </c>
@@ -2059,7 +2069,7 @@
         <v>40679580</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="16">
         <v>2021</v>
       </c>
@@ -2082,7 +2092,7 @@
         <v>39150298</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="13">
         <v>2021</v>
       </c>
@@ -2105,7 +2115,7 @@
         <v>20714145</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>2021</v>
       </c>
@@ -2128,7 +2138,7 @@
         <v>31511478</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="13">
         <v>2021</v>
       </c>
@@ -2151,7 +2161,7 @@
         <v>23803632</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="16">
         <v>2021</v>
       </c>
@@ -2174,7 +2184,7 @@
         <v>18855939</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="13">
         <v>2021</v>
       </c>
@@ -2197,7 +2207,7 @@
         <v>11133175</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="16">
         <v>2021</v>
       </c>
@@ -2220,7 +2230,7 @@
         <v>17483766</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="13">
         <v>2021</v>
       </c>
@@ -2243,7 +2253,7 @@
         <v>20440924</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="16">
         <v>2021</v>
       </c>
@@ -2266,7 +2276,7 @@
         <v>23839391</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="13">
         <v>2021</v>
       </c>
@@ -2289,7 +2299,7 @@
         <v>23518958</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="16">
         <v>2021</v>
       </c>
@@ -2312,7 +2322,7 @@
         <v>20471461</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="13">
         <v>2021</v>
       </c>
@@ -2335,7 +2345,7 @@
         <v>17642541</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="16">
         <v>2021</v>
       </c>
@@ -2358,7 +2368,7 @@
         <v>11250885</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="13">
         <v>2021</v>
       </c>
@@ -2381,7 +2391,7 @@
         <v>8807263</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="16">
         <v>2021</v>
       </c>
@@ -2404,7 +2414,7 @@
         <v>3911472</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="13">
         <v>2021</v>
       </c>
@@ -2427,7 +2437,7 @@
         <v>6165443</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="16">
         <v>2021</v>
       </c>
@@ -2450,7 +2460,7 @@
         <v>8548286</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="13">
         <v>2021</v>
       </c>
@@ -2473,7 +2483,7 @@
         <v>11176841</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="16">
         <v>2021</v>
       </c>
@@ -2496,7 +2506,7 @@
         <v>9708701</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="13">
         <v>2021</v>
       </c>
@@ -2519,7 +2529,7 @@
         <v>7644148</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="16">
         <v>2021</v>
       </c>
@@ -2542,7 +2552,7 @@
         <v>13058152</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="13">
         <v>2021</v>
       </c>
@@ -2565,7 +2575,7 @@
         <v>13719965</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="16">
         <v>2021</v>
       </c>
@@ -2588,7 +2598,7 @@
         <v>9306662</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="13">
         <v>2021</v>
       </c>
@@ -2611,7 +2621,7 @@
         <v>4111637</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="16">
         <v>2021</v>
       </c>
@@ -2634,7 +2644,7 @@
         <v>5571566</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="13">
         <v>2021</v>
       </c>
@@ -2657,7 +2667,7 @@
         <v>6548834</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="16">
         <v>2021</v>
       </c>
@@ -2680,7 +2690,7 @@
         <v>8583586</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="13">
         <v>2021</v>
       </c>
@@ -2703,7 +2713,7 @@
         <v>9206586</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="16">
         <v>2021</v>
       </c>
@@ -2726,7 +2736,7 @@
         <v>8623505</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="13">
         <v>2021</v>
       </c>
@@ -2749,7 +2759,7 @@
         <v>12106876</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="16">
         <v>2021</v>
       </c>
@@ -2772,7 +2782,7 @@
         <v>11150382</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="13">
         <v>2021</v>
       </c>
@@ -2795,7 +2805,7 @@
         <v>13642740</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="16">
         <v>2021</v>
       </c>
@@ -2818,7 +2828,7 @@
         <v>5521396</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="13">
         <v>2021</v>
       </c>
@@ -2841,7 +2851,7 @@
         <v>7480690</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="16">
         <v>2021</v>
       </c>
@@ -2864,7 +2874,7 @@
         <v>10154500</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="13">
         <v>2021</v>
       </c>
@@ -2887,7 +2897,7 @@
         <v>8054697</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="16">
         <v>2021</v>
       </c>
@@ -2910,7 +2920,7 @@
         <v>8411845</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="13">
         <v>2021</v>
       </c>
@@ -2933,7 +2943,7 @@
         <v>8753123</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="16">
         <v>2021</v>
       </c>
@@ -2956,7 +2966,7 @@
         <v>9117525</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="13">
         <v>2021</v>
       </c>
@@ -2979,7 +2989,7 @@
         <v>7460378</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="16">
         <v>2021</v>
       </c>
@@ -3002,7 +3012,7 @@
         <v>21282683</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="13">
         <v>2021</v>
       </c>
@@ -3025,7 +3035,7 @@
         <v>3068780</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="16">
         <v>2021</v>
       </c>
@@ -3048,7 +3058,7 @@
         <v>5689324</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="13">
         <v>2021</v>
       </c>
@@ -3071,7 +3081,7 @@
         <v>11293465</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="16">
         <v>2021</v>
       </c>
@@ -3094,7 +3104,7 @@
         <v>16136574</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="13">
         <v>2021</v>
       </c>
@@ -3117,7 +3127,7 @@
         <v>9391856</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="16">
         <v>2021</v>
       </c>
@@ -3140,7 +3150,7 @@
         <v>7838404</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="13">
         <v>2021</v>
       </c>
@@ -3163,7 +3173,7 @@
         <v>12858774</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="16">
         <v>2021</v>
       </c>
@@ -3186,7 +3196,7 @@
         <v>29177200</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="13">
         <v>2021</v>
       </c>
@@ -3209,7 +3219,7 @@
         <v>41690</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="16">
         <v>2021</v>
       </c>
@@ -3232,7 +3242,7 @@
         <v>23051</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="13">
         <v>2021</v>
       </c>
@@ -3255,7 +3265,7 @@
         <v>31931</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="16">
         <v>2021</v>
       </c>
@@ -3278,7 +3288,7 @@
         <v>35562</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="13">
         <v>2021</v>
       </c>
@@ -3301,7 +3311,7 @@
         <v>43238</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="16">
         <v>2021</v>
       </c>
@@ -3324,7 +3334,7 @@
         <v>50451</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="13">
         <v>2021</v>
       </c>
@@ -3347,7 +3357,7 @@
         <v>31773</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="16">
         <v>2021</v>
       </c>
@@ -3370,7 +3380,7 @@
         <v>36694</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="13">
         <v>2021</v>
       </c>
@@ -3393,7 +3403,7 @@
         <v>30073</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="16">
         <v>2021</v>
       </c>
@@ -3416,7 +3426,7 @@
         <v>51378</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="13">
         <v>2021</v>
       </c>
@@ -3439,7 +3449,7 @@
         <v>28991</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="16">
         <v>2021</v>
       </c>
@@ -3462,7 +3472,7 @@
         <v>41486</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="13">
         <v>2021</v>
       </c>
@@ -3485,7 +3495,7 @@
         <v>48942</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="16">
         <v>2021</v>
       </c>
@@ -3508,7 +3518,7 @@
         <v>56216</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="13">
         <v>2021</v>
       </c>
@@ -3531,7 +3541,7 @@
         <v>50362</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="16">
         <v>2021</v>
       </c>
@@ -3554,7 +3564,7 @@
         <v>38893</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="13">
         <v>2021</v>
       </c>
@@ -3577,7 +3587,7 @@
         <v>47947</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="16">
         <v>2021</v>
       </c>
@@ -3600,7 +3610,7 @@
         <v>24523</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="13">
         <v>2021</v>
       </c>
@@ -3623,7 +3633,7 @@
         <v>121947</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="16">
         <v>2021</v>
       </c>
@@ -3646,7 +3656,7 @@
         <v>64762</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="13">
         <v>2021</v>
       </c>
@@ -3669,7 +3679,7 @@
         <v>104679</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="16">
         <v>2021</v>
       </c>
@@ -3692,7 +3702,7 @@
         <v>143062</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="13">
         <v>2021</v>
       </c>
@@ -3715,7 +3725,7 @@
         <v>189947</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="16">
         <v>2021</v>
       </c>
@@ -3738,7 +3748,7 @@
         <v>134338</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="13">
         <v>2021</v>
       </c>
@@ -3761,7 +3771,7 @@
         <v>131533</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="16">
         <v>2021</v>
       </c>
@@ -3784,7 +3794,7 @@
         <v>132372</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="13">
         <v>2021</v>
       </c>
@@ -3807,7 +3817,7 @@
         <v>64518</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="16">
         <v>2021</v>
       </c>
@@ -3830,7 +3840,7 @@
         <v>195854</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="13">
         <v>2021</v>
       </c>
@@ -3853,7 +3863,7 @@
         <v>122313</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="16">
         <v>2021</v>
       </c>
@@ -3876,7 +3886,7 @@
         <v>219248</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="13">
         <v>2021</v>
       </c>
@@ -3899,7 +3909,7 @@
         <v>308401</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="16">
         <v>2021</v>
       </c>
@@ -3922,7 +3932,7 @@
         <v>354392</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="13">
         <v>2021</v>
       </c>
@@ -3945,7 +3955,7 @@
         <v>340468</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="16">
         <v>2021</v>
       </c>
@@ -3968,7 +3978,7 @@
         <v>249559</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="13">
         <v>2021</v>
       </c>
@@ -3991,7 +4001,7 @@
         <v>285985</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="16">
         <v>2021</v>
       </c>
@@ -4014,7 +4024,7 @@
         <v>136797</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="13">
         <v>2021</v>
       </c>
@@ -4037,7 +4047,7 @@
         <v>501412</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="16">
         <v>2021</v>
       </c>
@@ -4060,7 +4070,7 @@
         <v>178427</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="13">
         <v>2021</v>
       </c>
@@ -4083,7 +4093,7 @@
         <v>359896</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="16">
         <v>2021</v>
       </c>
@@ -4106,7 +4116,7 @@
         <v>765742</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="13">
         <v>2021</v>
       </c>
@@ -4129,7 +4139,7 @@
         <v>1100526</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="16">
         <v>2021</v>
       </c>
@@ -4152,7 +4162,7 @@
         <v>1043554</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="13">
         <v>2021</v>
       </c>
@@ -4175,7 +4185,7 @@
         <v>750724</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="16">
         <v>2021</v>
       </c>
@@ -4198,7 +4208,7 @@
         <v>975264</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="13">
         <v>2021</v>
       </c>
@@ -4221,7 +4231,7 @@
         <v>677247</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="16">
         <v>2021</v>
       </c>
@@ -4244,7 +4254,7 @@
         <v>829110</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="13">
         <v>2021</v>
       </c>
@@ -4267,7 +4277,7 @@
         <v>744753</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="16">
         <v>2021</v>
       </c>
@@ -4290,7 +4300,7 @@
         <v>1310680</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="13">
         <v>2021</v>
       </c>
@@ -4313,7 +4323,7 @@
         <v>1535401</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="16">
         <v>2021</v>
       </c>
@@ -4336,7 +4346,7 @@
         <v>2001685</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="13">
         <v>2021</v>
       </c>
@@ -4359,7 +4369,7 @@
         <v>1616477</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="16">
         <v>2021</v>
       </c>
@@ -4382,7 +4392,7 @@
         <v>1195648</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="13">
         <v>2021</v>
       </c>
@@ -4405,7 +4415,7 @@
         <v>1035131</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="16">
         <v>2021</v>
       </c>
@@ -4428,7 +4438,7 @@
         <v>717248</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="13">
         <v>2021</v>
       </c>
@@ -4451,7 +4461,7 @@
         <v>136665</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="16">
         <v>2021</v>
       </c>
@@ -4474,7 +4484,7 @@
         <v>124313</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="13">
         <v>2021</v>
       </c>
@@ -4497,7 +4507,7 @@
         <v>247535</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="16">
         <v>2021</v>
       </c>
@@ -4520,7 +4530,7 @@
         <v>436803</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="13">
         <v>2021</v>
       </c>
@@ -4543,7 +4553,7 @@
         <v>621770</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="16">
         <v>2021</v>
       </c>
@@ -4566,7 +4576,7 @@
         <v>415324</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="13">
         <v>2021</v>
       </c>
@@ -4589,7 +4599,7 @@
         <v>277012</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="16">
         <v>2021</v>
       </c>
@@ -4612,7 +4622,7 @@
         <v>617533</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="13">
         <v>2021</v>
       </c>
@@ -4635,7 +4645,7 @@
         <v>708811</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="16">
         <v>2021</v>
       </c>
@@ -4658,7 +4668,7 @@
         <v>90456</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="13">
         <v>2021</v>
       </c>
@@ -4681,7 +4691,7 @@
         <v>76968</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="16">
         <v>2021</v>
       </c>
@@ -4704,7 +4714,7 @@
         <v>100602</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="13">
         <v>2021</v>
       </c>
@@ -4727,7 +4737,7 @@
         <v>215547</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="16">
         <v>2021</v>
       </c>
@@ -4750,7 +4760,7 @@
         <v>302320</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="13">
         <v>2021</v>
       </c>
@@ -4773,7 +4783,7 @@
         <v>271460</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="16">
         <v>2021</v>
       </c>
@@ -4796,7 +4806,7 @@
         <v>223747</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="13">
         <v>2021</v>
       </c>
@@ -4819,7 +4829,7 @@
         <v>667598</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="16">
         <v>2021</v>
       </c>
@@ -4842,7 +4852,7 @@
         <v>783559</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="13">
         <v>2021</v>
       </c>
@@ -4865,7 +4875,7 @@
         <v>55518</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="16">
         <v>2021</v>
       </c>
@@ -4888,7 +4898,7 @@
         <v>41881</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="13">
         <v>2021</v>
       </c>
@@ -4911,7 +4921,7 @@
         <v>58458</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="16">
         <v>2021</v>
       </c>
@@ -4934,7 +4944,7 @@
         <v>122541</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="13">
         <v>2021</v>
       </c>
@@ -4957,7 +4967,7 @@
         <v>136850</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="16">
         <v>2021</v>
       </c>
@@ -4980,7 +4990,7 @@
         <v>172844</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="13">
         <v>2021</v>
       </c>
@@ -5003,7 +5013,7 @@
         <v>216501</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="16">
         <v>2021</v>
       </c>
@@ -5026,7 +5036,7 @@
         <v>491545</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="13">
         <v>2021</v>
       </c>
@@ -5049,7 +5059,7 @@
         <v>347128</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="16">
         <v>2021</v>
       </c>
@@ -5072,7 +5082,7 @@
         <v>29377</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="13">
         <v>2021</v>
       </c>
@@ -5095,7 +5105,7 @@
         <v>15682</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="16">
         <v>2021</v>
       </c>
@@ -5118,7 +5128,7 @@
         <v>30134</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="13">
         <v>2021</v>
       </c>
@@ -5141,7 +5151,7 @@
         <v>64473</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="16">
         <v>2021</v>
       </c>
@@ -5164,7 +5174,7 @@
         <v>130487</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="13">
         <v>2021</v>
       </c>
@@ -5187,7 +5197,7 @@
         <v>122600</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="16">
         <v>2021</v>
       </c>
@@ -5210,7 +5220,7 @@
         <v>86851</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="13">
         <v>2021</v>
       </c>
@@ -5233,7 +5243,7 @@
         <v>240510</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="16">
         <v>2021</v>
       </c>
@@ -5256,7 +5266,7 @@
         <v>400536</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="13">
         <v>2021</v>
       </c>
@@ -5279,7 +5289,7 @@
         <v>97132</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="16">
         <v>2021</v>
       </c>
@@ -5302,7 +5312,7 @@
         <v>37021</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="13">
         <v>2021</v>
       </c>
@@ -5325,7 +5335,7 @@
         <v>66290</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="16">
         <v>2021</v>
       </c>
@@ -5348,7 +5358,7 @@
         <v>69100</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="13">
         <v>2021</v>
       </c>
@@ -5371,7 +5381,7 @@
         <v>68659</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="16">
         <v>2021</v>
       </c>
@@ -5394,7 +5404,7 @@
         <v>60045</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="13">
         <v>2021</v>
       </c>
@@ -5417,7 +5427,7 @@
         <v>45343</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="16">
         <v>2021</v>
       </c>
@@ -5440,7 +5450,7 @@
         <v>39056</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="13">
         <v>2021</v>
       </c>
@@ -5463,7 +5473,7 @@
         <v>46924</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="16">
         <v>2021</v>
       </c>
@@ -5486,7 +5496,7 @@
         <v>123029</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="13">
         <v>2021</v>
       </c>
@@ -5509,7 +5519,7 @@
         <v>50803</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="16">
         <v>2021</v>
       </c>
@@ -5532,7 +5542,7 @@
         <v>86678</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="13">
         <v>2021</v>
       </c>
@@ -5555,7 +5565,7 @@
         <v>83936</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="16">
         <v>2021</v>
       </c>
@@ -5578,7 +5588,7 @@
         <v>85455</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="13">
         <v>2021</v>
       </c>
@@ -5601,7 +5611,7 @@
         <v>73581</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="16">
         <v>2021</v>
       </c>
@@ -5624,7 +5634,7 @@
         <v>59564</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="13">
         <v>2021</v>
       </c>
@@ -5647,7 +5657,7 @@
         <v>49359</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="16">
         <v>2021</v>
       </c>
@@ -5670,7 +5680,7 @@
         <v>34170</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="13">
         <v>2021</v>
       </c>
@@ -5693,7 +5703,7 @@
         <v>320407</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="16">
         <v>2021</v>
       </c>
@@ -5716,7 +5726,7 @@
         <v>110136</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="13">
         <v>2021</v>
       </c>
@@ -5739,7 +5749,7 @@
         <v>233693</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="16">
         <v>2021</v>
       </c>
@@ -5762,7 +5772,7 @@
         <v>252665</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="13">
         <v>2021</v>
       </c>
@@ -5785,7 +5795,7 @@
         <v>262297</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="16">
         <v>2021</v>
       </c>
@@ -5808,7 +5818,7 @@
         <v>230867</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="13">
         <v>2021</v>
       </c>
@@ -5831,7 +5841,7 @@
         <v>173537</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="16">
         <v>2021</v>
       </c>
@@ -5854,7 +5864,7 @@
         <v>143541</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="13">
         <v>2021</v>
       </c>
@@ -5877,7 +5887,7 @@
         <v>89641</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="16">
         <v>2021</v>
       </c>
@@ -5900,7 +5910,7 @@
         <v>712695</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="13">
         <v>2021</v>
       </c>
@@ -5923,7 +5933,7 @@
         <v>222387</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="16">
         <v>2021</v>
       </c>
@@ -5946,7 +5956,7 @@
         <v>435126</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="13">
         <v>2021</v>
       </c>
@@ -5969,7 +5979,7 @@
         <v>545849</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="16">
         <v>2021</v>
       </c>
@@ -5992,7 +6002,7 @@
         <v>577522</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="13">
         <v>2021</v>
       </c>
@@ -6015,7 +6025,7 @@
         <v>532652</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="16">
         <v>2021</v>
       </c>
@@ -6038,7 +6048,7 @@
         <v>397332</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="13">
         <v>2021</v>
       </c>
@@ -6061,7 +6071,7 @@
         <v>397875</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="16">
         <v>2021</v>
       </c>
@@ -6084,7 +6094,7 @@
         <v>214256</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="13">
         <v>2021</v>
       </c>
@@ -6107,7 +6117,7 @@
         <v>1826009</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="16">
         <v>2021</v>
       </c>
@@ -6130,7 +6140,7 @@
         <v>529900</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="13">
         <v>2021</v>
       </c>
@@ -6153,7 +6163,7 @@
         <v>1205240</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="16">
         <v>2021</v>
       </c>
@@ -6176,7 +6186,7 @@
         <v>1736815</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="13">
         <v>2021</v>
       </c>
@@ -6199,7 +6209,7 @@
         <v>2739082</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="16">
         <v>2021</v>
       </c>
@@ -6222,7 +6232,7 @@
         <v>2214697</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="13">
         <v>2021</v>
       </c>
@@ -6245,7 +6255,7 @@
         <v>1073138</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="16">
         <v>2021</v>
       </c>
@@ -6268,7 +6278,7 @@
         <v>1644249</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="13">
         <v>2021</v>
       </c>
@@ -6291,7 +6301,7 @@
         <v>785281</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="16">
         <v>2021</v>
       </c>
@@ -6314,7 +6324,7 @@
         <v>1359597</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="13">
         <v>2021</v>
       </c>
@@ -6337,7 +6347,7 @@
         <v>864619</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="16">
         <v>2021</v>
       </c>
@@ -6360,7 +6370,7 @@
         <v>2038793</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="13">
         <v>2021</v>
       </c>
@@ -6383,7 +6393,7 @@
         <v>1912967</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="16">
         <v>2021</v>
       </c>
@@ -6406,7 +6416,7 @@
         <v>2013458</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="13">
         <v>2021</v>
       </c>
@@ -6429,7 +6439,7 @@
         <v>1947743</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="16">
         <v>2021</v>
       </c>
@@ -6452,7 +6462,7 @@
         <v>1644908</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="13">
         <v>2021</v>
       </c>
@@ -6475,7 +6485,7 @@
         <v>1294358</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="16">
         <v>2021</v>
       </c>
@@ -6498,7 +6508,7 @@
         <v>768068</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="13">
         <v>2021</v>
       </c>
@@ -6521,7 +6531,7 @@
         <v>697516</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="16">
         <v>2021</v>
       </c>
@@ -6544,7 +6554,7 @@
         <v>326521</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="13">
         <v>2021</v>
       </c>
@@ -6567,7 +6577,7 @@
         <v>613326</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="16">
         <v>2021</v>
       </c>
@@ -6590,7 +6600,7 @@
         <v>737615</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="13">
         <v>2021</v>
       </c>
@@ -6613,7 +6623,7 @@
         <v>932025</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="16">
         <v>2021</v>
       </c>
@@ -6636,7 +6646,7 @@
         <v>837315</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="13">
         <v>2021</v>
       </c>
@@ -6659,7 +6669,7 @@
         <v>543390</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="16">
         <v>2021</v>
       </c>
@@ -6682,7 +6692,7 @@
         <v>883116</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="13">
         <v>2021</v>
       </c>
@@ -6705,7 +6715,7 @@
         <v>912909</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="16">
         <v>2021</v>
       </c>
@@ -6728,7 +6738,7 @@
         <v>533234</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="13">
         <v>2021</v>
       </c>
@@ -6751,7 +6761,7 @@
         <v>289763</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="16">
         <v>2021</v>
       </c>
@@ -6774,7 +6784,7 @@
         <v>473607</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="13">
         <v>2021</v>
       </c>
@@ -6797,7 +6807,7 @@
         <v>462228</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="16">
         <v>2021</v>
       </c>
@@ -6820,7 +6830,7 @@
         <v>531267</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="13">
         <v>2021</v>
       </c>
@@ -6843,7 +6853,7 @@
         <v>544736</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="16">
         <v>2021</v>
       </c>
@@ -6866,7 +6876,7 @@
         <v>554545</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="13">
         <v>2021</v>
       </c>
@@ -6889,7 +6899,7 @@
         <v>656635</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="16">
         <v>2021</v>
       </c>
@@ -6912,7 +6922,7 @@
         <v>454533</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="13">
         <v>2021</v>
       </c>
@@ -6935,7 +6945,7 @@
         <v>387672</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="16">
         <v>2021</v>
       </c>
@@ -6958,7 +6968,7 @@
         <v>164618</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="13">
         <v>2021</v>
       </c>
@@ -6981,7 +6991,7 @@
         <v>429290</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="16">
         <v>2021</v>
       </c>
@@ -7004,7 +7014,7 @@
         <v>762430</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="13">
         <v>2021</v>
       </c>
@@ -7027,7 +7037,7 @@
         <v>541369</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="16">
         <v>2021</v>
       </c>
@@ -7050,7 +7060,7 @@
         <v>662222</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="13">
         <v>2021</v>
       </c>
@@ -7073,7 +7083,7 @@
         <v>782166</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="16">
         <v>2021</v>
       </c>
@@ -7096,7 +7106,7 @@
         <v>636014</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="13">
         <v>2021</v>
       </c>
@@ -7119,7 +7129,7 @@
         <v>421709</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="16">
         <v>2021</v>
       </c>
@@ -7142,7 +7152,7 @@
         <v>139792</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="13">
         <v>2021</v>
       </c>
@@ -7165,7 +7175,7 @@
         <v>47914</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="16">
         <v>2021</v>
       </c>
@@ -7188,7 +7198,7 @@
         <v>145531</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="13">
         <v>2021</v>
       </c>
@@ -7211,7 +7221,7 @@
         <v>441489</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="16">
         <v>2021</v>
       </c>
@@ -7234,7 +7244,7 @@
         <v>712832</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="13">
         <v>2021</v>
       </c>
@@ -7257,7 +7267,7 @@
         <v>543056</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="16">
         <v>2021</v>
       </c>
@@ -7280,7 +7290,7 @@
         <v>366103</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="13">
         <v>2021</v>
       </c>
@@ -7303,7 +7313,7 @@
         <v>512293</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="16">
         <v>2021</v>
       </c>
@@ -7326,7 +7336,7 @@
         <v>1137919</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="13">
         <v>2021</v>
       </c>
@@ -7349,7 +7359,7 @@
         <v>315134</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="16">
         <v>2021</v>
       </c>
@@ -7372,7 +7382,7 @@
         <v>122071</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="13">
         <v>2021</v>
       </c>
@@ -7395,7 +7405,7 @@
         <v>148195</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="16">
         <v>2021</v>
       </c>
@@ -7418,7 +7428,7 @@
         <v>158405</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="13">
         <v>2021</v>
       </c>
@@ -7441,7 +7451,7 @@
         <v>151844</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="16">
         <v>2021</v>
       </c>
@@ -7464,7 +7474,7 @@
         <v>160596</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="13">
         <v>2021</v>
       </c>
@@ -7487,7 +7497,7 @@
         <v>141306</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="16">
         <v>2021</v>
       </c>
@@ -7510,7 +7520,7 @@
         <v>145078</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="13">
         <v>2021</v>
       </c>
@@ -7533,7 +7543,7 @@
         <v>141550</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="16">
         <v>2021</v>
       </c>
@@ -7556,7 +7566,7 @@
         <v>367396</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="13">
         <v>2021</v>
       </c>
@@ -7579,7 +7589,7 @@
         <v>138565</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="16">
         <v>2021</v>
       </c>
@@ -7602,7 +7612,7 @@
         <v>159979</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="13">
         <v>2021</v>
       </c>
@@ -7625,7 +7635,7 @@
         <v>187572</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="16">
         <v>2021</v>
       </c>
@@ -7648,7 +7658,7 @@
         <v>202291</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="13">
         <v>2021</v>
       </c>
@@ -7671,7 +7681,7 @@
         <v>209261</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="16">
         <v>2021</v>
       </c>
@@ -7694,7 +7704,7 @@
         <v>161040</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="13">
         <v>2021</v>
       </c>
@@ -7717,7 +7727,7 @@
         <v>171064</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="16">
         <v>2021</v>
       </c>
@@ -7740,7 +7750,7 @@
         <v>124467</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="13">
         <v>2021</v>
       </c>
@@ -7763,7 +7773,7 @@
         <v>1055782</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="16">
         <v>2021</v>
       </c>
@@ -7786,7 +7796,7 @@
         <v>360318</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="13">
         <v>2021</v>
       </c>
@@ -7809,7 +7819,7 @@
         <v>413531</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="16">
         <v>2021</v>
       </c>
@@ -7832,7 +7842,7 @@
         <v>534846</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="13">
         <v>2021</v>
       </c>
@@ -7855,7 +7865,7 @@
         <v>617233</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="16">
         <v>2021</v>
       </c>
@@ -7878,7 +7888,7 @@
         <v>618464</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="13">
         <v>2021</v>
       </c>
@@ -7901,7 +7911,7 @@
         <v>558219</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="16">
         <v>2021</v>
       </c>
@@ -7924,7 +7934,7 @@
         <v>584600</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="13">
         <v>2021</v>
       </c>
@@ -7947,7 +7957,7 @@
         <v>326762</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="16">
         <v>2021</v>
       </c>
@@ -7970,7 +7980,7 @@
         <v>2309658</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="13">
         <v>2021</v>
       </c>
@@ -7993,7 +8003,7 @@
         <v>673488</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="16">
         <v>2021</v>
       </c>
@@ -8016,7 +8026,7 @@
         <v>862386</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="13">
         <v>2021</v>
       </c>
@@ -8039,7 +8049,7 @@
         <v>1209456</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="16">
         <v>2021</v>
       </c>
@@ -8062,7 +8072,7 @@
         <v>1471087</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="13">
         <v>2021</v>
       </c>
@@ -8085,7 +8095,7 @@
         <v>1510019</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="16">
         <v>2021</v>
       </c>
@@ -8108,7 +8118,7 @@
         <v>1219234</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="13">
         <v>2021</v>
       </c>
@@ -8131,7 +8141,7 @@
         <v>1381420</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="16">
         <v>2021</v>
       </c>
@@ -8154,7 +8164,7 @@
         <v>793067</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="13">
         <v>2021</v>
       </c>
@@ -8177,7 +8187,7 @@
         <v>5904653</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="16">
         <v>2021</v>
       </c>
@@ -8200,7 +8210,7 @@
         <v>1942399</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="13">
         <v>2021</v>
       </c>
@@ -8223,7 +8233,7 @@
         <v>2496472</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="16">
         <v>2021</v>
       </c>
@@ -8246,7 +8256,7 @@
         <v>4299589</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="13">
         <v>2021</v>
       </c>
@@ -8269,7 +8279,7 @@
         <v>7650492</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="16">
         <v>2021</v>
       </c>
@@ -8292,7 +8302,7 @@
         <v>7125779</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="13">
         <v>2021</v>
       </c>
@@ -8315,7 +8325,7 @@
         <v>4263428</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="16">
         <v>2021</v>
       </c>
@@ -8338,7 +8348,7 @@
         <v>5332037</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" s="13">
         <v>2021</v>
       </c>
@@ -8361,7 +8371,7 @@
         <v>3190232</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" s="16">
         <v>2021</v>
       </c>
@@ -8384,7 +8394,7 @@
         <v>6820439</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" s="13">
         <v>2021</v>
       </c>
@@ -8407,7 +8417,7 @@
         <v>3877828</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="16">
         <v>2021</v>
       </c>
@@ -8430,7 +8440,7 @@
         <v>4204538</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" s="13">
         <v>2021</v>
       </c>
@@ -8453,7 +8463,7 @@
         <v>5486568</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="16">
         <v>2021</v>
       </c>
@@ -8476,7 +8486,7 @@
         <v>6816198</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="13">
         <v>2021</v>
       </c>
@@ -8499,7 +8509,7 @@
         <v>6964730</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" s="16">
         <v>2021</v>
       </c>
@@ -8522,7 +8532,7 @@
         <v>5894448</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" s="13">
         <v>2021</v>
       </c>
@@ -8545,7 +8555,7 @@
         <v>4807293</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" s="16">
         <v>2021</v>
       </c>
@@ -8568,7 +8578,7 @@
         <v>3256581</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="13">
         <v>2021</v>
       </c>
@@ -8591,7 +8601,7 @@
         <v>2529241</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" s="16">
         <v>2021</v>
       </c>
@@ -8614,7 +8624,7 @@
         <v>1094844</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" s="13">
         <v>2021</v>
       </c>
@@ -8637,7 +8647,7 @@
         <v>1278399</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" s="16">
         <v>2021</v>
       </c>
@@ -8660,7 +8670,7 @@
         <v>2009828</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="13">
         <v>2021</v>
       </c>
@@ -8683,7 +8693,7 @@
         <v>2731923</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" s="16">
         <v>2021</v>
       </c>
@@ -8706,7 +8716,7 @@
         <v>2569077</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" s="13">
         <v>2021</v>
       </c>
@@ -8729,7 +8739,7 @@
         <v>2123136</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" s="16">
         <v>2021</v>
       </c>
@@ -8752,7 +8762,7 @@
         <v>3502222</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="13">
         <v>2021</v>
       </c>
@@ -8775,7 +8785,7 @@
         <v>3314317</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="16">
         <v>2021</v>
       </c>
@@ -8798,7 +8808,7 @@
         <v>2363200</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" s="13">
         <v>2021</v>
       </c>
@@ -8821,7 +8831,7 @@
         <v>830435</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="16">
         <v>2021</v>
       </c>
@@ -8844,7 +8854,7 @@
         <v>902304</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="13">
         <v>2021</v>
       </c>
@@ -8867,7 +8877,7 @@
         <v>1248738</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="16">
         <v>2021</v>
       </c>
@@ -8890,7 +8900,7 @@
         <v>1738031</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="13">
         <v>2021</v>
       </c>
@@ -8913,7 +8923,7 @@
         <v>1972144</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="16">
         <v>2021</v>
       </c>
@@ -8936,7 +8946,7 @@
         <v>1971550</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="13">
         <v>2021</v>
       </c>
@@ -8959,7 +8969,7 @@
         <v>2926580</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="16">
         <v>2021</v>
       </c>
@@ -8982,7 +8992,7 @@
         <v>2409862</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="13">
         <v>2021</v>
       </c>
@@ -9005,7 +9015,7 @@
         <v>1798562</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="16">
         <v>2021</v>
       </c>
@@ -9028,7 +9038,7 @@
         <v>544353</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="13">
         <v>2021</v>
       </c>
@@ -9051,7 +9061,7 @@
         <v>811582</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="16">
         <v>2021</v>
       </c>
@@ -9074,7 +9084,7 @@
         <v>1450103</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="13">
         <v>2021</v>
       </c>
@@ -9097,7 +9107,7 @@
         <v>1323053</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="16">
         <v>2021</v>
       </c>
@@ -9120,7 +9130,7 @@
         <v>1330466</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="13">
         <v>2021</v>
       </c>
@@ -9143,7 +9153,7 @@
         <v>1700312</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="16">
         <v>2021</v>
       </c>
@@ -9166,7 +9176,7 @@
         <v>1934746</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="13">
         <v>2021</v>
       </c>
@@ -9189,7 +9199,7 @@
         <v>1217090</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="16">
         <v>2021</v>
       </c>
@@ -9212,7 +9222,7 @@
         <v>1180309</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" s="13">
         <v>2021</v>
       </c>
@@ -9235,7 +9245,7 @@
         <v>208912</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" s="16">
         <v>2021</v>
       </c>
@@ -9258,7 +9268,7 @@
         <v>344735</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" s="13">
         <v>2021</v>
       </c>
@@ -9281,7 +9291,7 @@
         <v>902995</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" s="16">
         <v>2021</v>
       </c>
@@ -9304,7 +9314,7 @@
         <v>1793305</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" s="13">
         <v>2021</v>
       </c>
@@ -9327,7 +9337,7 @@
         <v>1132145</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" s="16">
         <v>2021</v>
       </c>
@@ -9350,7 +9360,7 @@
         <v>1118581</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" s="13">
         <v>2021</v>
       </c>
@@ -9373,7 +9383,7 @@
         <v>2020047</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="16">
         <v>2021</v>
       </c>
@@ -9396,7 +9406,7 @@
         <v>3544223</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="13">
         <v>2021</v>
       </c>
@@ -9419,7 +9429,7 @@
         <v>129659</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" s="16">
         <v>2021</v>
       </c>
@@ -9442,7 +9452,7 @@
         <v>46436</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" s="13">
         <v>2021</v>
       </c>
@@ -9465,7 +9475,7 @@
         <v>93020</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="16">
         <v>2021</v>
       </c>
@@ -9488,7 +9498,7 @@
         <v>98433</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" s="13">
         <v>2021</v>
       </c>
@@ -9511,7 +9521,7 @@
         <v>101834</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" s="16">
         <v>2021</v>
       </c>
@@ -9534,7 +9544,7 @@
         <v>106217</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" s="13">
         <v>2021</v>
       </c>
@@ -9557,7 +9567,7 @@
         <v>87528</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" s="16">
         <v>2021</v>
       </c>
@@ -9580,7 +9590,7 @@
         <v>90848</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" s="13">
         <v>2021</v>
       </c>
@@ -9603,7 +9613,7 @@
         <v>123057</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" s="16">
         <v>2021</v>
       </c>
@@ -9626,7 +9636,7 @@
         <v>185157</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" s="13">
         <v>2021</v>
       </c>
@@ -9649,7 +9659,7 @@
         <v>69618</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" s="16">
         <v>2021</v>
       </c>
@@ -9672,7 +9682,7 @@
         <v>127601</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" s="13">
         <v>2021</v>
       </c>
@@ -9695,7 +9705,7 @@
         <v>128716</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="16">
         <v>2021</v>
       </c>
@@ -9718,7 +9728,7 @@
         <v>129969</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" s="13">
         <v>2021</v>
       </c>
@@ -9741,7 +9751,7 @@
         <v>126625</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" s="16">
         <v>2021</v>
       </c>
@@ -9764,7 +9774,7 @@
         <v>96275</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" s="13">
         <v>2021</v>
       </c>
@@ -9787,7 +9797,7 @@
         <v>111527</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="16">
         <v>2021</v>
       </c>
@@ -9810,7 +9820,7 @@
         <v>109419</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="13">
         <v>2021</v>
       </c>
@@ -9833,7 +9843,7 @@
         <v>656566</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" s="16">
         <v>2021</v>
       </c>
@@ -9856,7 +9866,7 @@
         <v>183893</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="13">
         <v>2021</v>
       </c>
@@ -9879,7 +9889,7 @@
         <v>354465</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="16">
         <v>2021</v>
       </c>
@@ -9902,7 +9912,7 @@
         <v>428964</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" s="13">
         <v>2021</v>
       </c>
@@ -9925,7 +9935,7 @@
         <v>475252</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="16">
         <v>2021</v>
       </c>
@@ -9948,7 +9958,7 @@
         <v>445222</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="13">
         <v>2021</v>
       </c>
@@ -9971,7 +9981,7 @@
         <v>382083</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="16">
         <v>2021</v>
       </c>
@@ -9994,7 +10004,7 @@
         <v>396344</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="13">
         <v>2021</v>
       </c>
@@ -10017,7 +10027,7 @@
         <v>309341</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="16">
         <v>2021</v>
       </c>
@@ -10040,7 +10050,7 @@
         <v>1667598</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="13">
         <v>2021</v>
       </c>
@@ -10063,7 +10073,7 @@
         <v>393075</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="16">
         <v>2021</v>
       </c>
@@ -10086,7 +10096,7 @@
         <v>837225</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="13">
         <v>2021</v>
       </c>
@@ -10109,7 +10119,7 @@
         <v>1014554</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="16">
         <v>2021</v>
       </c>
@@ -10132,7 +10142,7 @@
         <v>1338470</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="13">
         <v>2021</v>
       </c>
@@ -10155,7 +10165,7 @@
         <v>1214941</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="16">
         <v>2021</v>
       </c>
@@ -10178,7 +10188,7 @@
         <v>937643</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="13">
         <v>2021</v>
       </c>
@@ -10201,7 +10211,7 @@
         <v>1132451</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="16">
         <v>2021</v>
       </c>
@@ -10224,7 +10234,7 @@
         <v>759491</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="13">
         <v>2021</v>
       </c>
@@ -10247,7 +10257,7 @@
         <v>5147912</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="16">
         <v>2021</v>
       </c>
@@ -10270,7 +10280,7 @@
         <v>1858703</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="13">
         <v>2021</v>
       </c>
@@ -10293,7 +10303,7 @@
         <v>3340057</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="16">
         <v>2021</v>
       </c>
@@ -10316,7 +10326,7 @@
         <v>5379509</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="13">
         <v>2021</v>
       </c>
@@ -10339,7 +10349,7 @@
         <v>8082760</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="16">
         <v>2021</v>
       </c>
@@ -10362,7 +10372,7 @@
         <v>7631775</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="13">
         <v>2021</v>
       </c>
@@ -10385,7 +10395,7 @@
         <v>4143588</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="16">
         <v>2021</v>
       </c>
@@ -10408,7 +10418,7 @@
         <v>6740353</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="13">
         <v>2021</v>
       </c>
@@ -10431,7 +10441,7 @@
         <v>4603486</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="16">
         <v>2021</v>
       </c>
@@ -10454,7 +10464,7 @@
         <v>2994288</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="13">
         <v>2021</v>
       </c>
@@ -10477,7 +10487,7 @@
         <v>1419101</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="16">
         <v>2021</v>
       </c>
@@ -10500,7 +10510,7 @@
         <v>3118121</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="13">
         <v>2021</v>
       </c>
@@ -10523,7 +10533,7 @@
         <v>3422052</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="16">
         <v>2021</v>
       </c>
@@ -10546,7 +10556,7 @@
         <v>4015482</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="13">
         <v>2021</v>
       </c>
@@ -10569,7 +10579,7 @@
         <v>3920377</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="16">
         <v>2021</v>
       </c>
@@ -10592,7 +10602,7 @@
         <v>3626342</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="13">
         <v>2021</v>
       </c>
@@ -10615,7 +10625,7 @@
         <v>2908144</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="16">
         <v>2021</v>
       </c>
@@ -10638,7 +10648,7 @@
         <v>2099518</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="13">
         <v>2021</v>
       </c>
@@ -10661,7 +10671,7 @@
         <v>1930761</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="16">
         <v>2021</v>
       </c>
@@ -10684,7 +10694,7 @@
         <v>708052</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="13">
         <v>2021</v>
       </c>
@@ -10707,7 +10717,7 @@
         <v>1489951</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="16">
         <v>2021</v>
       </c>
@@ -10730,7 +10740,7 @@
         <v>1942327</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="13">
         <v>2021</v>
       </c>
@@ -10753,7 +10763,7 @@
         <v>2668378</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="16">
         <v>2021</v>
       </c>
@@ -10776,7 +10786,7 @@
         <v>2332687</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="13">
         <v>2021</v>
       </c>
@@ -10799,7 +10809,7 @@
         <v>1685150</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="16">
         <v>2021</v>
       </c>
@@ -10822,7 +10832,7 @@
         <v>2908478</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="13">
         <v>2021</v>
       </c>
@@ -10845,7 +10855,7 @@
         <v>3446777</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="16">
         <v>2021</v>
       </c>
@@ -10868,7 +10878,7 @@
         <v>1885493</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="13">
         <v>2021</v>
       </c>
@@ -10891,7 +10901,7 @@
         <v>881496</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="16">
         <v>2021</v>
       </c>
@@ -10914,7 +10924,7 @@
         <v>1223293</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="13">
         <v>2021</v>
       </c>
@@ -10937,7 +10947,7 @@
         <v>1465664</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="16">
         <v>2021</v>
       </c>
@@ -10960,7 +10970,7 @@
         <v>2256844</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="13">
         <v>2021</v>
       </c>
@@ -10983,7 +10993,7 @@
         <v>2560623</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="16">
         <v>2021</v>
       </c>
@@ -11006,7 +11016,7 @@
         <v>2287675</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="13">
         <v>2021</v>
       </c>
@@ -11029,7 +11039,7 @@
         <v>3060990</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="16">
         <v>2021</v>
       </c>
@@ -11052,7 +11062,7 @@
         <v>3046477</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="13">
         <v>2021</v>
       </c>
@@ -11075,7 +11085,7 @@
         <v>1900774</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="16">
         <v>2021</v>
       </c>
@@ -11098,7 +11108,7 @@
         <v>1178761</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="13">
         <v>2021</v>
       </c>
@@ -11121,7 +11131,7 @@
         <v>1552350</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="16">
         <v>2021</v>
       </c>
@@ -11144,7 +11154,7 @@
         <v>1654869</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="13">
         <v>2021</v>
       </c>
@@ -11167,7 +11177,7 @@
         <v>1691584</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="16">
         <v>2021</v>
       </c>
@@ -11190,7 +11200,7 @@
         <v>1785279</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="13">
         <v>2021</v>
       </c>
@@ -11213,7 +11223,7 @@
         <v>1928495</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="16">
         <v>2021</v>
       </c>
@@ -11236,7 +11246,7 @@
         <v>1674316</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="13">
         <v>2021</v>
       </c>
@@ -11259,7 +11269,7 @@
         <v>1413724</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="16">
         <v>2021</v>
       </c>
@@ -11282,7 +11292,7 @@
         <v>2116103</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="13">
         <v>2021</v>
       </c>
@@ -11305,7 +11315,7 @@
         <v>488221</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="16">
         <v>2021</v>
       </c>
@@ -11328,7 +11338,7 @@
         <v>1071835</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="13">
         <v>2021</v>
       </c>
@@ -11351,7 +11361,7 @@
         <v>1747149</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="16">
         <v>2021</v>
       </c>
@@ -11374,7 +11384,7 @@
         <v>2673620</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="13">
         <v>2021</v>
       </c>
@@ -11397,7 +11407,7 @@
         <v>1530327</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="16">
         <v>2021</v>
       </c>
@@ -11420,7 +11430,7 @@
         <v>1087172</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="13">
         <v>2021</v>
       </c>
@@ -11443,7 +11453,7 @@
         <v>1484197</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="16">
         <v>2021</v>
       </c>
@@ -11466,7 +11476,7 @@
         <v>3618407</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="13">
         <v>2021</v>
       </c>
@@ -11489,7 +11499,7 @@
         <v>44412</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="16">
         <v>2021</v>
       </c>
@@ -11512,7 +11522,7 @@
         <v>23593</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="13">
         <v>2021</v>
       </c>
@@ -11535,7 +11545,7 @@
         <v>50018</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="16">
         <v>2021</v>
       </c>
@@ -11558,7 +11568,7 @@
         <v>39559</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="13">
         <v>2021</v>
       </c>
@@ -11581,7 +11591,7 @@
         <v>42224</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="16">
         <v>2021</v>
       </c>
@@ -11604,7 +11614,7 @@
         <v>41726</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="13">
         <v>2021</v>
       </c>
@@ -11627,7 +11637,7 @@
         <v>42726</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="16">
         <v>2021</v>
       </c>
@@ -11650,7 +11660,7 @@
         <v>57051</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="13">
         <v>2021</v>
       </c>
@@ -11673,7 +11683,7 @@
         <v>55501</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="16">
         <v>2021</v>
       </c>
@@ -11696,7 +11706,7 @@
         <v>59830</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="13">
         <v>2021</v>
       </c>
@@ -11719,7 +11729,7 @@
         <v>37933</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="16">
         <v>2021</v>
       </c>
@@ -11742,7 +11752,7 @@
         <v>66365</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="13">
         <v>2021</v>
       </c>
@@ -11765,7 +11775,7 @@
         <v>65244</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="16">
         <v>2021</v>
       </c>
@@ -11788,7 +11798,7 @@
         <v>65800</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="13">
         <v>2021</v>
       </c>
@@ -11811,7 +11821,7 @@
         <v>58029</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="16">
         <v>2021</v>
       </c>
@@ -11834,7 +11844,7 @@
         <v>53419</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="13">
         <v>2021</v>
       </c>
@@ -11857,7 +11867,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="16">
         <v>2021</v>
       </c>
@@ -11880,7 +11890,7 @@
         <v>37660</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="13">
         <v>2021</v>
       </c>
@@ -11903,7 +11913,7 @@
         <v>202455</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="16">
         <v>2021</v>
       </c>
@@ -11926,7 +11936,7 @@
         <v>99317</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="13">
         <v>2021</v>
       </c>
@@ -11949,7 +11959,7 @@
         <v>188882</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="16">
         <v>2021</v>
       </c>
@@ -11972,7 +11982,7 @@
         <v>213260</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="13">
         <v>2021</v>
       </c>
@@ -11995,7 +12005,7 @@
         <v>243925</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="16">
         <v>2021</v>
       </c>
@@ -12018,7 +12028,7 @@
         <v>226156</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="13">
         <v>2021</v>
       </c>
@@ -12041,7 +12051,7 @@
         <v>180221</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="16">
         <v>2021</v>
       </c>
@@ -12064,7 +12074,7 @@
         <v>162727</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="13">
         <v>2021</v>
       </c>
@@ -12087,7 +12097,7 @@
         <v>99321</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="16">
         <v>2021</v>
       </c>
@@ -12110,7 +12120,7 @@
         <v>580533</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A480" s="13">
         <v>2021</v>
       </c>
@@ -12133,7 +12143,7 @@
         <v>188823</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A481" s="16">
         <v>2021</v>
       </c>
@@ -12156,7 +12166,7 @@
         <v>402177</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A482" s="13">
         <v>2021</v>
       </c>
@@ -12179,7 +12189,7 @@
         <v>526794</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A483" s="16">
         <v>2021</v>
       </c>
@@ -12202,7 +12212,7 @@
         <v>725473</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A484" s="13">
         <v>2021</v>
       </c>
@@ -12225,7 +12235,7 @@
         <v>542350</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A485" s="16">
         <v>2021</v>
       </c>
@@ -12248,7 +12258,7 @@
         <v>439390</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A486" s="13">
         <v>2021</v>
       </c>
@@ -12271,7 +12281,7 @@
         <v>440149</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A487" s="16">
         <v>2021</v>
       </c>
@@ -12294,7 +12304,7 @@
         <v>253878</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A488" s="13">
         <v>2021</v>
       </c>
@@ -12317,7 +12327,7 @@
         <v>2049895</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A489" s="16">
         <v>2021</v>
       </c>
@@ -12340,7 +12350,7 @@
         <v>708433</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A490" s="13">
         <v>2021</v>
       </c>
@@ -12363,7 +12373,7 @@
         <v>1325716</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A491" s="16">
         <v>2021</v>
       </c>
@@ -12386,7 +12396,7 @@
         <v>2078854</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A492" s="13">
         <v>2021</v>
       </c>
@@ -12409,7 +12419,7 @@
         <v>3316641</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A493" s="16">
         <v>2021</v>
       </c>
@@ -12432,7 +12442,7 @@
         <v>3554581</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A494" s="13">
         <v>2021</v>
       </c>
@@ -12455,7 +12465,7 @@
         <v>1344880</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A495" s="16">
         <v>2021</v>
       </c>
@@ -12478,7 +12488,7 @@
         <v>1952775</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A496" s="13">
         <v>2021</v>
       </c>
@@ -12501,7 +12511,7 @@
         <v>1464552</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A497" s="16">
         <v>2021</v>
       </c>
@@ -12524,7 +12534,7 @@
         <v>607482</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A498" s="13">
         <v>2021</v>
       </c>
@@ -12547,7 +12557,7 @@
         <v>485281</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A499" s="16">
         <v>2021</v>
       </c>
@@ -12570,7 +12580,7 @@
         <v>1116161</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A500" s="13">
         <v>2021</v>
       </c>
@@ -12593,7 +12603,7 @@
         <v>1180520</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A501" s="16">
         <v>2021</v>
       </c>
@@ -12616,7 +12626,7 @@
         <v>1419030</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A502" s="13">
         <v>2021</v>
       </c>
@@ -12639,7 +12649,7 @@
         <v>1346423</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A503" s="16">
         <v>2021</v>
       </c>
@@ -12662,7 +12672,7 @@
         <v>1313436</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A504" s="13">
         <v>2021</v>
       </c>
@@ -12685,7 +12695,7 @@
         <v>890449</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A505" s="16">
         <v>2021</v>
       </c>
@@ -12708,7 +12718,7 @@
         <v>468689</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A506" s="13">
         <v>2021</v>
       </c>
@@ -12731,7 +12741,7 @@
         <v>369079</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A507" s="16">
         <v>2021</v>
       </c>
@@ -12754,7 +12764,7 @@
         <v>250526</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A508" s="13">
         <v>2021</v>
       </c>
@@ -12777,7 +12787,7 @@
         <v>496022</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A509" s="16">
         <v>2021</v>
       </c>
@@ -12800,7 +12810,7 @@
         <v>621763</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A510" s="13">
         <v>2021</v>
       </c>
@@ -12823,7 +12833,7 @@
         <v>830599</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A511" s="16">
         <v>2021</v>
       </c>
@@ -12846,7 +12856,7 @@
         <v>637545</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A512" s="13">
         <v>2021</v>
       </c>
@@ -12869,7 +12879,7 @@
         <v>515049</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A513" s="16">
         <v>2021</v>
       </c>
@@ -12892,7 +12902,7 @@
         <v>718940</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A514" s="13">
         <v>2021</v>
       </c>
@@ -12915,7 +12925,7 @@
         <v>866115</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A515" s="16">
         <v>2021</v>
       </c>
@@ -12938,7 +12948,7 @@
         <v>411112</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A516" s="13">
         <v>2021</v>
       </c>
@@ -12961,7 +12971,7 @@
         <v>266859</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A517" s="16">
         <v>2021</v>
       </c>
@@ -12984,7 +12994,7 @@
         <v>458747</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A518" s="13">
         <v>2021</v>
       </c>
@@ -13007,7 +13017,7 @@
         <v>562639</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A519" s="16">
         <v>2021</v>
       </c>
@@ -13030,7 +13040,7 @@
         <v>819320</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A520" s="13">
         <v>2021</v>
       </c>
@@ -13053,7 +13063,7 @@
         <v>790260</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A521" s="16">
         <v>2021</v>
       </c>
@@ -13076,7 +13086,7 @@
         <v>694394</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A522" s="13">
         <v>2021</v>
       </c>
@@ -13099,7 +13109,7 @@
         <v>850025</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A523" s="16">
         <v>2021</v>
       </c>
@@ -13122,7 +13132,7 @@
         <v>925611</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A524" s="13">
         <v>2021</v>
       </c>
@@ -13145,7 +13155,7 @@
         <v>463599</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A525" s="16">
         <v>2021</v>
       </c>
@@ -13168,7 +13178,7 @@
         <v>191827</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A526" s="13">
         <v>2021</v>
       </c>
@@ -13191,7 +13201,7 @@
         <v>425823</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A527" s="16">
         <v>2021</v>
       </c>
@@ -13214,7 +13224,7 @@
         <v>706928</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A528" s="13">
         <v>2021</v>
       </c>
@@ -13237,7 +13247,7 @@
         <v>826852</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A529" s="16">
         <v>2021</v>
       </c>
@@ -13260,7 +13270,7 @@
         <v>789467</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A530" s="13">
         <v>2021</v>
       </c>
@@ -13283,7 +13293,7 @@
         <v>705231</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A531" s="16">
         <v>2021</v>
       </c>
@@ -13306,7 +13316,7 @@
         <v>711302</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A532" s="13">
         <v>2021</v>
       </c>
@@ -13329,7 +13339,7 @@
         <v>754532</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A533" s="16">
         <v>2021</v>
       </c>
@@ -13352,7 +13362,7 @@
         <v>222576</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A534" s="13">
         <v>2021</v>
       </c>
@@ -13375,7 +13385,7 @@
         <v>76058</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A535" s="16">
         <v>2021</v>
       </c>
@@ -13398,7 +13408,7 @@
         <v>267104</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A536" s="13">
         <v>2021</v>
       </c>
@@ -13421,7 +13431,7 @@
         <v>814639</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A537" s="16">
         <v>2021</v>
       </c>
@@ -13444,7 +13454,7 @@
         <v>1109504</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A538" s="13">
         <v>2021</v>
       </c>
@@ -13467,7 +13477,7 @@
         <v>398496</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A539" s="16">
         <v>2021</v>
       </c>
@@ -13490,7 +13500,7 @@
         <v>335699</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A540" s="13">
         <v>2021</v>
       </c>
@@ -13513,7 +13523,7 @@
         <v>731444</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A541" s="16">
         <v>2021</v>
       </c>
@@ -13536,7 +13546,7 @@
         <v>1752499</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A542" s="13">
         <v>2021</v>
       </c>
@@ -13559,7 +13569,7 @@
         <v>170133</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A543" s="16">
         <v>2021</v>
       </c>
@@ -13582,7 +13592,7 @@
         <v>64782</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A544" s="13">
         <v>2021</v>
       </c>
@@ -13605,7 +13615,7 @@
         <v>95725</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A545" s="16">
         <v>2021</v>
       </c>
@@ -13628,7 +13638,7 @@
         <v>109523</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A546" s="13">
         <v>2021</v>
       </c>
@@ -13651,7 +13661,7 @@
         <v>109057</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A547" s="16">
         <v>2021</v>
       </c>
@@ -13674,7 +13684,7 @@
         <v>109758</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A548" s="13">
         <v>2021</v>
       </c>
@@ -13697,7 +13707,7 @@
         <v>112827</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A549" s="16">
         <v>2021</v>
       </c>
@@ -13720,7 +13730,7 @@
         <v>123486</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A550" s="13">
         <v>2021</v>
       </c>
@@ -13743,7 +13753,7 @@
         <v>118456</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A551" s="16">
         <v>2021</v>
       </c>
@@ -13766,7 +13776,7 @@
         <v>212547</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A552" s="13">
         <v>2021</v>
       </c>
@@ -13789,7 +13799,7 @@
         <v>70662</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A553" s="16">
         <v>2021</v>
       </c>
@@ -13812,7 +13822,7 @@
         <v>110666</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A554" s="13">
         <v>2021</v>
       </c>
@@ -13835,7 +13845,7 @@
         <v>136791</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A555" s="16">
         <v>2021</v>
       </c>
@@ -13858,7 +13868,7 @@
         <v>139500</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A556" s="13">
         <v>2021</v>
       </c>
@@ -13881,7 +13891,7 @@
         <v>126559</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A557" s="16">
         <v>2021</v>
       </c>
@@ -13904,7 +13914,7 @@
         <v>118732</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A558" s="13">
         <v>2021</v>
       </c>
@@ -13927,7 +13937,7 @@
         <v>133456</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A559" s="16">
         <v>2021</v>
       </c>
@@ -13950,7 +13960,7 @@
         <v>88186</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A560" s="13">
         <v>2021</v>
       </c>
@@ -13973,7 +13983,7 @@
         <v>675914</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A561" s="16">
         <v>2021</v>
       </c>
@@ -13996,7 +14006,7 @@
         <v>163839</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A562" s="13">
         <v>2021</v>
       </c>
@@ -14019,7 +14029,7 @@
         <v>324716</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A563" s="16">
         <v>2021</v>
       </c>
@@ -14042,7 +14052,7 @@
         <v>381944</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A564" s="13">
         <v>2021</v>
       </c>
@@ -14065,7 +14075,7 @@
         <v>446477</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A565" s="16">
         <v>2021</v>
       </c>
@@ -14088,7 +14098,7 @@
         <v>426470</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A566" s="13">
         <v>2021</v>
       </c>
@@ -14111,7 +14121,7 @@
         <v>394513</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A567" s="16">
         <v>2021</v>
       </c>
@@ -14134,7 +14144,7 @@
         <v>425569</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A568" s="13">
         <v>2021</v>
       </c>
@@ -14157,7 +14167,7 @@
         <v>218440</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A569" s="16">
         <v>2021</v>
       </c>
@@ -14180,7 +14190,7 @@
         <v>1596618</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A570" s="13">
         <v>2021</v>
       </c>
@@ -14203,7 +14213,7 @@
         <v>387982</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A571" s="16">
         <v>2021</v>
       </c>
@@ -14226,7 +14236,7 @@
         <v>622274</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A572" s="13">
         <v>2021</v>
       </c>
@@ -14249,7 +14259,7 @@
         <v>804641</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A573" s="16">
         <v>2021</v>
       </c>
@@ -14272,7 +14282,7 @@
         <v>1027819</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A574" s="13">
         <v>2021</v>
       </c>
@@ -14295,7 +14305,7 @@
         <v>991589</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A575" s="16">
         <v>2021</v>
       </c>
@@ -14318,7 +14328,7 @@
         <v>840641</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A576" s="13">
         <v>2021</v>
       </c>
@@ -14341,7 +14351,7 @@
         <v>973404</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A577" s="16">
         <v>2021</v>
       </c>
@@ -14364,7 +14374,7 @@
         <v>537369</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A578" s="13">
         <v>2021</v>
       </c>
@@ -14387,7 +14397,7 @@
         <v>4824608</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A579" s="16">
         <v>2021</v>
       </c>
@@ -14410,7 +14420,7 @@
         <v>1467539</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A580" s="13">
         <v>2021</v>
       </c>
@@ -14433,7 +14443,7 @@
         <v>2548238</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A581" s="16">
         <v>2021</v>
       </c>
@@ -14456,7 +14466,7 @@
         <v>3290449</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A582" s="13">
         <v>2021</v>
       </c>
@@ -14479,7 +14489,7 @@
         <v>5411325</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A583" s="16">
         <v>2021</v>
       </c>
@@ -14502,7 +14512,7 @@
         <v>4793425</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A584" s="13">
         <v>2021</v>
       </c>
@@ -14525,7 +14535,7 @@
         <v>2863476</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A585" s="16">
         <v>2021</v>
       </c>
@@ -14548,7 +14558,7 @@
         <v>5531235</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A586" s="13">
         <v>2021</v>
       </c>
@@ -14571,7 +14581,7 @@
         <v>3188337</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A587" s="16">
         <v>2021</v>
       </c>
@@ -14594,7 +14604,7 @@
         <v>3520683</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A588" s="13">
         <v>2021</v>
       </c>
@@ -14617,7 +14627,7 @@
         <v>1524991</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A589" s="16">
         <v>2021</v>
       </c>
@@ -14640,7 +14650,7 @@
         <v>2911838</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A590" s="13">
         <v>2021</v>
       </c>
@@ -14663,7 +14673,7 @@
         <v>3609799</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A591" s="16">
         <v>2021</v>
       </c>
@@ -14686,7 +14696,7 @@
         <v>4123047</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A592" s="13">
         <v>2021</v>
       </c>
@@ -14709,7 +14719,7 @@
         <v>3786545</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A593" s="16">
         <v>2021</v>
       </c>
@@ -14732,7 +14742,7 @@
         <v>3139958</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A594" s="13">
         <v>2021</v>
       </c>
@@ -14755,7 +14765,7 @@
         <v>2909259</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A595" s="16">
         <v>2021</v>
       </c>
@@ -14778,7 +14788,7 @@
         <v>1851958</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A596" s="13">
         <v>2021</v>
       </c>
@@ -14801,7 +14811,7 @@
         <v>1465987</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A597" s="16">
         <v>2021</v>
       </c>
@@ -14824,7 +14834,7 @@
         <v>586651</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A598" s="13">
         <v>2021</v>
       </c>
@@ -14847,7 +14857,7 @@
         <v>875299</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A599" s="16">
         <v>2021</v>
       </c>
@@ -14870,7 +14880,7 @@
         <v>1304281</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A600" s="13">
         <v>2021</v>
       </c>
@@ -14893,7 +14903,7 @@
         <v>1733582</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A601" s="16">
         <v>2021</v>
       </c>
@@ -14916,7 +14926,7 @@
         <v>1477983</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A602" s="13">
         <v>2021</v>
       </c>
@@ -14939,7 +14949,7 @@
         <v>1302935</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A603" s="16">
         <v>2021</v>
       </c>
@@ -14962,7 +14972,7 @@
         <v>2215196</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A604" s="13">
         <v>2021</v>
       </c>
@@ -14985,7 +14995,7 @@
         <v>2043203</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A605" s="16">
         <v>2021</v>
       </c>
@@ -15008,7 +15018,7 @@
         <v>1559544</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A606" s="13">
         <v>2021</v>
       </c>
@@ -15031,7 +15041,7 @@
         <v>644061</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A607" s="16">
         <v>2021</v>
       </c>
@@ -15054,7 +15064,7 @@
         <v>824649</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A608" s="13">
         <v>2021</v>
       </c>
@@ -15077,7 +15087,7 @@
         <v>875039</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A609" s="16">
         <v>2021</v>
       </c>
@@ -15100,7 +15110,7 @@
         <v>1249104</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A610" s="13">
         <v>2021</v>
       </c>
@@ -15123,7 +15133,7 @@
         <v>1467915</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A611" s="16">
         <v>2021</v>
       </c>
@@ -15146,7 +15156,7 @@
         <v>1447608</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A612" s="13">
         <v>2021</v>
       </c>
@@ -15169,7 +15179,7 @@
         <v>1810441</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A613" s="16">
         <v>2021</v>
       </c>
@@ -15192,7 +15202,7 @@
         <v>1471425</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A614" s="13">
         <v>2021</v>
       </c>
@@ -15215,7 +15225,7 @@
         <v>1993024</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A615" s="16">
         <v>2021</v>
       </c>
@@ -15238,7 +15248,7 @@
         <v>539936</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A616" s="13">
         <v>2021</v>
       </c>
@@ -15261,7 +15271,7 @@
         <v>993109</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A617" s="16">
         <v>2021</v>
       </c>
@@ -15284,7 +15294,7 @@
         <v>1217516</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A618" s="13">
         <v>2021</v>
       </c>
@@ -15307,7 +15317,7 @@
         <v>1071391</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A619" s="16">
         <v>2021</v>
       </c>
@@ -15330,7 +15340,7 @@
         <v>1282062</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A620" s="13">
         <v>2021</v>
       </c>
@@ -15353,7 +15363,7 @@
         <v>1117425</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A621" s="16">
         <v>2021</v>
       </c>
@@ -15376,7 +15386,7 @@
         <v>1122973</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A622" s="13">
         <v>2021</v>
       </c>
@@ -15399,7 +15409,7 @@
         <v>1054927</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A623" s="16">
         <v>2021</v>
       </c>
@@ -15422,7 +15432,7 @@
         <v>1383824</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A624" s="13">
         <v>2021</v>
       </c>
@@ -15445,7 +15455,7 @@
         <v>167090</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A625" s="16">
         <v>2021</v>
       </c>
@@ -15468,7 +15478,7 @@
         <v>438365</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A626" s="13">
         <v>2021</v>
       </c>
@@ -15491,7 +15501,7 @@
         <v>1333693</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A627" s="16">
         <v>2021</v>
       </c>
@@ -15514,7 +15524,7 @@
         <v>2306802</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A628" s="13">
         <v>2021</v>
       </c>
@@ -15537,7 +15547,7 @@
         <v>668701</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A629" s="16">
         <v>2021</v>
       </c>
@@ -15560,7 +15570,7 @@
         <v>481445</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A630" s="13">
         <v>2021</v>
       </c>
@@ -15583,7 +15593,7 @@
         <v>778497</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A631" s="16">
         <v>2021</v>
       </c>
@@ -15606,7 +15616,7 @@
         <v>3037130</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A632" s="13">
         <v>2021</v>
       </c>
@@ -15629,7 +15639,7 @@
         <v>95969</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A633" s="16">
         <v>2021</v>
       </c>
@@ -15652,7 +15662,7 @@
         <v>28752</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A634" s="13">
         <v>2021</v>
       </c>
@@ -15675,7 +15685,7 @@
         <v>51253</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A635" s="16">
         <v>2021</v>
       </c>
@@ -15698,7 +15708,7 @@
         <v>59614</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A636" s="13">
         <v>2021</v>
       </c>
@@ -15721,7 +15731,7 @@
         <v>66243</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A637" s="16">
         <v>2021</v>
       </c>
@@ -15744,7 +15754,7 @@
         <v>60801</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A638" s="13">
         <v>2021</v>
       </c>
@@ -15767,7 +15777,7 @@
         <v>56598</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A639" s="16">
         <v>2021</v>
       </c>
@@ -15790,7 +15800,7 @@
         <v>59073</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A640" s="13">
         <v>2021</v>
       </c>
@@ -15813,7 +15823,7 @@
         <v>50775</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A641" s="16">
         <v>2021</v>
       </c>
@@ -15836,7 +15846,7 @@
         <v>91631</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A642" s="13">
         <v>2021</v>
       </c>
@@ -15859,7 +15869,7 @@
         <v>42713</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A643" s="16">
         <v>2021</v>
       </c>
@@ -15882,7 +15892,7 @@
         <v>77622</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A644" s="13">
         <v>2021</v>
       </c>
@@ -15905,7 +15915,7 @@
         <v>87550</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A645" s="16">
         <v>2021</v>
       </c>
@@ -15928,7 +15938,7 @@
         <v>89884</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A646" s="13">
         <v>2021</v>
       </c>
@@ -15951,7 +15961,7 @@
         <v>74587</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A647" s="16">
         <v>2021</v>
       </c>
@@ -15974,7 +15984,7 @@
         <v>76069</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A648" s="13">
         <v>2021</v>
       </c>
@@ -15997,7 +16007,7 @@
         <v>73545</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A649" s="16">
         <v>2021</v>
       </c>
@@ -16020,7 +16030,7 @@
         <v>42990</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A650" s="13">
         <v>2021</v>
       </c>
@@ -16043,7 +16053,7 @@
         <v>305211</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A651" s="16">
         <v>2021</v>
       </c>
@@ -16066,7 +16076,7 @@
         <v>114788</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A652" s="13">
         <v>2021</v>
       </c>
@@ -16089,7 +16099,7 @@
         <v>212124</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A653" s="16">
         <v>2021</v>
       </c>
@@ -16112,7 +16122,7 @@
         <v>293796</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A654" s="13">
         <v>2021</v>
       </c>
@@ -16135,7 +16145,7 @@
         <v>313281</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A655" s="16">
         <v>2021</v>
       </c>
@@ -16158,7 +16168,7 @@
         <v>311670</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A656" s="13">
         <v>2021</v>
       </c>
@@ -16181,7 +16191,7 @@
         <v>246650</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A657" s="16">
         <v>2021</v>
       </c>
@@ -16204,7 +16214,7 @@
         <v>268354</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A658" s="13">
         <v>2021</v>
       </c>
@@ -16227,7 +16237,7 @@
         <v>149040</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A659" s="16">
         <v>2021</v>
       </c>
@@ -16250,7 +16260,7 @@
         <v>692929</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A660" s="13">
         <v>2021</v>
       </c>
@@ -16273,7 +16283,7 @@
         <v>279226</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A661" s="16">
         <v>2021</v>
       </c>
@@ -16296,7 +16306,7 @@
         <v>535500</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A662" s="13">
         <v>2021</v>
       </c>
@@ -16319,7 +16329,7 @@
         <v>783484</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A663" s="16">
         <v>2021</v>
       </c>
@@ -16342,7 +16352,7 @@
         <v>938387</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A664" s="13">
         <v>2021</v>
       </c>
@@ -16365,7 +16375,7 @@
         <v>772190</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A665" s="16">
         <v>2021</v>
       </c>
@@ -16388,7 +16398,7 @@
         <v>601963</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A666" s="13">
         <v>2021</v>
       </c>
@@ -16411,7 +16421,7 @@
         <v>663003</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A667" s="16">
         <v>2021</v>
       </c>
@@ -16434,7 +16444,7 @@
         <v>389956</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A668" s="13">
         <v>2021</v>
       </c>
@@ -16457,7 +16467,7 @@
         <v>2501196</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A669" s="16">
         <v>2021</v>
       </c>
@@ -16480,7 +16490,7 @@
         <v>813102</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A670" s="13">
         <v>2021</v>
       </c>
@@ -16503,7 +16513,7 @@
         <v>1676293</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A671" s="16">
         <v>2021</v>
       </c>
@@ -16526,7 +16536,7 @@
         <v>3015256</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A672" s="13">
         <v>2021</v>
       </c>
@@ -16549,7 +16559,7 @@
         <v>4610621</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A673" s="16">
         <v>2021</v>
       </c>
@@ -16572,7 +16582,7 @@
         <v>3970428</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A674" s="13">
         <v>2021</v>
       </c>
@@ -16595,7 +16605,7 @@
         <v>2256691</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A675" s="16">
         <v>2021</v>
       </c>
@@ -16618,7 +16628,7 @@
         <v>3833012</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A676" s="13">
         <v>2021</v>
       </c>
@@ -16641,7 +16651,7 @@
         <v>2398268</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A677" s="16">
         <v>2021</v>
       </c>
@@ -16664,7 +16674,7 @@
         <v>1322380</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A678" s="13">
         <v>2021</v>
       </c>
@@ -16687,7 +16697,7 @@
         <v>529374</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A679" s="16">
         <v>2021</v>
       </c>
@@ -16710,7 +16720,7 @@
         <v>1189024</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A680" s="13">
         <v>2021</v>
       </c>
@@ -16733,7 +16743,7 @@
         <v>1549032</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A681" s="16">
         <v>2021</v>
       </c>
@@ -16756,7 +16766,7 @@
         <v>1639089</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A682" s="13">
         <v>2021</v>
       </c>
@@ -16779,7 +16789,7 @@
         <v>1685094</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A683" s="16">
         <v>2021</v>
       </c>
@@ -16802,7 +16812,7 @@
         <v>1668224</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A684" s="13">
         <v>2021</v>
       </c>
@@ -16825,7 +16835,7 @@
         <v>1471186</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A685" s="16">
         <v>2021</v>
       </c>
@@ -16848,7 +16858,7 @@
         <v>662805</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A686" s="13">
         <v>2021</v>
       </c>
@@ -16871,7 +16881,7 @@
         <v>741332</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A687" s="16">
         <v>2021</v>
       </c>
@@ -16894,7 +16904,7 @@
         <v>360209</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A688" s="13">
         <v>2021</v>
       </c>
@@ -16917,7 +16927,7 @@
         <v>617529</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A689" s="16">
         <v>2021</v>
       </c>
@@ -16940,7 +16950,7 @@
         <v>905543</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A690" s="13">
         <v>2021</v>
       </c>
@@ -16963,7 +16973,7 @@
         <v>1032645</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A691" s="16">
         <v>2021</v>
       </c>
@@ -16986,7 +16996,7 @@
         <v>888305</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A692" s="13">
         <v>2021</v>
       </c>
@@ -17009,7 +17019,7 @@
         <v>728812</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A693" s="16">
         <v>2021</v>
       </c>
@@ -17032,7 +17042,7 @@
         <v>1284332</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A694" s="13">
         <v>2021</v>
       </c>
@@ -17055,7 +17065,7 @@
         <v>1330818</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A695" s="16">
         <v>2021</v>
       </c>
@@ -17078,7 +17088,7 @@
         <v>810257</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A696" s="13">
         <v>2021</v>
       </c>
@@ -17101,7 +17111,7 @@
         <v>433309</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A697" s="16">
         <v>2021</v>
       </c>
@@ -17124,7 +17134,7 @@
         <v>648052</v>
       </c>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A698" s="13">
         <v>2021</v>
       </c>
@@ -17147,7 +17157,7 @@
         <v>884428</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A699" s="16">
         <v>2021</v>
       </c>
@@ -17170,7 +17180,7 @@
         <v>1002189</v>
       </c>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A700" s="13">
         <v>2021</v>
       </c>
@@ -17193,7 +17203,7 @@
         <v>950776</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A701" s="16">
         <v>2021</v>
       </c>
@@ -17216,7 +17226,7 @@
         <v>823797</v>
       </c>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A702" s="13">
         <v>2021</v>
       </c>
@@ -17239,7 +17249,7 @@
         <v>1323417</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A703" s="16">
         <v>2021</v>
       </c>
@@ -17262,7 +17272,7 @@
         <v>1361383</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A704" s="13">
         <v>2021</v>
       </c>
@@ -17285,7 +17295,7 @@
         <v>901645</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A705" s="16">
         <v>2021</v>
       </c>
@@ -17308,7 +17318,7 @@
         <v>437876</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A706" s="13">
         <v>2021</v>
       </c>
@@ -17331,7 +17341,7 @@
         <v>578698</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A707" s="16">
         <v>2021</v>
       </c>
@@ -17354,7 +17364,7 @@
         <v>894015</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A708" s="13">
         <v>2021</v>
       </c>
@@ -17377,7 +17387,7 @@
         <v>889761</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A709" s="16">
         <v>2021</v>
       </c>
@@ -17400,7 +17410,7 @@
         <v>905682</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A710" s="13">
         <v>2021</v>
       </c>
@@ -17423,7 +17433,7 @@
         <v>994393</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A711" s="16">
         <v>2021</v>
       </c>
@@ -17446,7 +17456,7 @@
         <v>1359929</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A712" s="13">
         <v>2021</v>
       </c>
@@ -17469,7 +17479,7 @@
         <v>1113770</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A713" s="16">
         <v>2021</v>
       </c>
@@ -17492,7 +17502,7 @@
         <v>750148</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A714" s="13">
         <v>2021</v>
       </c>
@@ -17515,7 +17525,7 @@
         <v>270508</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A715" s="16">
         <v>2021</v>
       </c>
@@ -17538,7 +17548,7 @@
         <v>401223</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A716" s="13">
         <v>2021</v>
       </c>
@@ -17561,7 +17571,7 @@
         <v>868867</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A717" s="16">
         <v>2021</v>
       </c>
@@ -17584,7 +17594,7 @@
         <v>1314399</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A718" s="13">
         <v>2021</v>
       </c>
@@ -17607,7 +17617,7 @@
         <v>923291</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A719" s="16">
         <v>2021</v>
       </c>
@@ -17630,7 +17640,7 @@
         <v>897702</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A720" s="13">
         <v>2021</v>
       </c>
@@ -17653,7 +17663,7 @@
         <v>1539409</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A721" s="16">
         <v>2021</v>
       </c>
@@ -17676,7 +17686,7 @@
         <v>2818662</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A722" s="13">
         <v>2021</v>
       </c>
@@ -17699,7 +17709,7 @@
         <v>36796</v>
       </c>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A723" s="16">
         <v>2021</v>
       </c>
@@ -17722,7 +17732,7 @@
         <v>16680</v>
       </c>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A724" s="13">
         <v>2021</v>
       </c>
@@ -17745,7 +17755,7 @@
         <v>26951</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A725" s="16">
         <v>2021</v>
       </c>
@@ -17768,7 +17778,7 @@
         <v>31743</v>
       </c>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A726" s="13">
         <v>2021</v>
       </c>
@@ -17791,7 +17801,7 @@
         <v>30023</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A727" s="16">
         <v>2021</v>
       </c>
@@ -17814,7 +17824,7 @@
         <v>25632</v>
       </c>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A728" s="13">
         <v>2021</v>
       </c>
@@ -17837,7 +17847,7 @@
         <v>24511</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A729" s="16">
         <v>2021</v>
       </c>
@@ -17860,7 +17870,7 @@
         <v>20515</v>
       </c>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A730" s="13">
         <v>2021</v>
       </c>
@@ -17883,7 +17893,7 @@
         <v>24470</v>
       </c>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A731" s="16">
         <v>2021</v>
       </c>
@@ -17906,7 +17916,7 @@
         <v>59460</v>
       </c>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A732" s="13">
         <v>2021</v>
       </c>
@@ -17929,7 +17939,7 @@
         <v>17760</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A733" s="16">
         <v>2021</v>
       </c>
@@ -17952,7 +17962,7 @@
         <v>34600</v>
       </c>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A734" s="13">
         <v>2021</v>
       </c>
@@ -17975,7 +17985,7 @@
         <v>48589</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A735" s="16">
         <v>2021</v>
       </c>
@@ -17998,7 +18008,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A736" s="13">
         <v>2021</v>
       </c>
@@ -18021,7 +18031,7 @@
         <v>38724</v>
       </c>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A737" s="16">
         <v>2021</v>
       </c>
@@ -18044,7 +18054,7 @@
         <v>32407</v>
       </c>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A738" s="13">
         <v>2021</v>
       </c>
@@ -18067,7 +18077,7 @@
         <v>28273</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A739" s="16">
         <v>2021</v>
       </c>
@@ -18090,7 +18100,7 @@
         <v>19962</v>
       </c>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A740" s="13">
         <v>2021</v>
       </c>
@@ -18113,7 +18123,7 @@
         <v>164453</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A741" s="16">
         <v>2021</v>
       </c>
@@ -18136,7 +18146,7 @@
         <v>57063</v>
       </c>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A742" s="13">
         <v>2021</v>
       </c>
@@ -18159,7 +18169,7 @@
         <v>107747</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A743" s="16">
         <v>2021</v>
       </c>
@@ -18182,7 +18192,7 @@
         <v>127346</v>
       </c>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A744" s="13">
         <v>2021</v>
       </c>
@@ -18205,7 +18215,7 @@
         <v>134468</v>
       </c>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A745" s="16">
         <v>2021</v>
       </c>
@@ -18228,7 +18238,7 @@
         <v>131510</v>
       </c>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A746" s="13">
         <v>2021</v>
       </c>
@@ -18251,7 +18261,7 @@
         <v>113252</v>
       </c>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A747" s="16">
         <v>2021</v>
       </c>
@@ -18274,7 +18284,7 @@
         <v>119944</v>
       </c>
     </row>
-    <row r="748" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A748" s="13">
         <v>2021</v>
       </c>
@@ -18297,7 +18307,7 @@
         <v>59813</v>
       </c>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A749" s="16">
         <v>2021</v>
       </c>
@@ -18320,7 +18330,7 @@
         <v>393876</v>
       </c>
     </row>
-    <row r="750" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A750" s="13">
         <v>2021</v>
       </c>
@@ -18343,7 +18353,7 @@
         <v>133690</v>
       </c>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A751" s="16">
         <v>2021</v>
       </c>
@@ -18366,7 +18376,7 @@
         <v>261214</v>
       </c>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A752" s="13">
         <v>2021</v>
       </c>
@@ -18389,7 +18399,7 @@
         <v>314845</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A753" s="16">
         <v>2021</v>
       </c>
@@ -18412,7 +18422,7 @@
         <v>329607</v>
       </c>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A754" s="13">
         <v>2021</v>
       </c>
@@ -18435,7 +18445,7 @@
         <v>318832</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A755" s="16">
         <v>2021</v>
       </c>
@@ -18458,7 +18468,7 @@
         <v>225987</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A756" s="13">
         <v>2021</v>
       </c>
@@ -18481,7 +18491,7 @@
         <v>312799</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A757" s="16">
         <v>2021</v>
       </c>
@@ -18504,7 +18514,7 @@
         <v>159176</v>
       </c>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A758" s="13">
         <v>2021</v>
       </c>
@@ -18527,7 +18537,7 @@
         <v>977336</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A759" s="16">
         <v>2021</v>
       </c>
@@ -18550,7 +18560,7 @@
         <v>395624</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A760" s="13">
         <v>2021</v>
       </c>
@@ -18573,7 +18583,7 @@
         <v>726126</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A761" s="16">
         <v>2021</v>
       </c>
@@ -18596,7 +18606,7 @@
         <v>1345259</v>
       </c>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A762" s="13">
         <v>2021</v>
       </c>
@@ -18619,7 +18629,7 @@
         <v>2296494</v>
       </c>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A763" s="16">
         <v>2021</v>
       </c>
@@ -18642,7 +18652,7 @@
         <v>1669902</v>
       </c>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A764" s="13">
         <v>2021</v>
       </c>
@@ -18665,7 +18675,7 @@
         <v>875459</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A765" s="16">
         <v>2021</v>
       </c>
@@ -18688,7 +18698,7 @@
         <v>1368517</v>
       </c>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A766" s="13">
         <v>2021</v>
       </c>
@@ -18711,7 +18721,7 @@
         <v>1009798</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A767" s="16">
         <v>2021</v>
       </c>
@@ -18734,7 +18744,7 @@
         <v>970774</v>
       </c>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A768" s="13">
         <v>2021</v>
       </c>
@@ -18757,7 +18767,7 @@
         <v>348225</v>
       </c>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A769" s="16">
         <v>2021</v>
       </c>
@@ -18780,7 +18790,7 @@
         <v>776138</v>
       </c>
     </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A770" s="13">
         <v>2021</v>
       </c>
@@ -18803,7 +18813,7 @@
         <v>980908</v>
       </c>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A771" s="16">
         <v>2021</v>
       </c>
@@ -18826,7 +18836,7 @@
         <v>995797</v>
       </c>
     </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A772" s="13">
         <v>2021</v>
       </c>
@@ -18849,7 +18859,7 @@
         <v>1055709</v>
       </c>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A773" s="16">
         <v>2021</v>
       </c>
@@ -18872,7 +18882,7 @@
         <v>1088268</v>
       </c>
     </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A774" s="13">
         <v>2021</v>
       </c>
@@ -18895,7 +18905,7 @@
         <v>958538</v>
       </c>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A775" s="16">
         <v>2021</v>
       </c>
@@ -18918,7 +18928,7 @@
         <v>500863</v>
       </c>
     </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A776" s="13">
         <v>2021</v>
       </c>
@@ -18941,7 +18951,7 @@
         <v>475887</v>
       </c>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A777" s="16">
         <v>2021</v>
       </c>
@@ -18964,7 +18974,7 @@
         <v>207996</v>
       </c>
     </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A778" s="13">
         <v>2021</v>
       </c>
@@ -18987,7 +18997,7 @@
         <v>316933</v>
       </c>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A779" s="16">
         <v>2021</v>
       </c>
@@ -19010,7 +19020,7 @@
         <v>401424</v>
       </c>
     </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A780" s="13">
         <v>2021</v>
       </c>
@@ -19033,7 +19043,7 @@
         <v>438225</v>
       </c>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A781" s="16">
         <v>2021</v>
       </c>
@@ -19056,7 +19066,7 @@
         <v>382795</v>
       </c>
     </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A782" s="13">
         <v>2021</v>
       </c>
@@ -19079,7 +19089,7 @@
         <v>342409</v>
       </c>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A783" s="16">
         <v>2021</v>
       </c>
@@ -19102,7 +19112,7 @@
         <v>583574</v>
       </c>
     </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A784" s="13">
         <v>2021</v>
       </c>
@@ -19125,7 +19135,7 @@
         <v>660398</v>
       </c>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A785" s="16">
         <v>2021</v>
       </c>
@@ -19148,7 +19158,7 @@
         <v>473295</v>
       </c>
     </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A786" s="13">
         <v>2021</v>
       </c>
@@ -19171,7 +19181,7 @@
         <v>230103</v>
       </c>
     </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A787" s="16">
         <v>2021</v>
       </c>
@@ -19194,7 +19204,7 @@
         <v>252415</v>
       </c>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A788" s="13">
         <v>2021</v>
       </c>
@@ -19217,7 +19227,7 @@
         <v>336840</v>
       </c>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A789" s="16">
         <v>2021</v>
       </c>
@@ -19240,7 +19250,7 @@
         <v>406672</v>
       </c>
     </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A790" s="13">
         <v>2021</v>
       </c>
@@ -19263,7 +19273,7 @@
         <v>411075</v>
       </c>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A791" s="16">
         <v>2021</v>
       </c>
@@ -19286,7 +19296,7 @@
         <v>429581</v>
       </c>
     </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A792" s="13">
         <v>2021</v>
       </c>
@@ -19309,7 +19319,7 @@
         <v>516868</v>
       </c>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A793" s="16">
         <v>2021</v>
       </c>
@@ -19332,7 +19342,7 @@
         <v>402092</v>
       </c>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A794" s="13">
         <v>2021</v>
       </c>
@@ -19355,7 +19365,7 @@
         <v>299921</v>
       </c>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A795" s="16">
         <v>2021</v>
       </c>
@@ -19378,7 +19388,7 @@
         <v>98700</v>
       </c>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A796" s="13">
         <v>2021</v>
       </c>
@@ -19401,7 +19411,7 @@
         <v>198106</v>
       </c>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A797" s="16">
         <v>2021</v>
       </c>
@@ -19424,7 +19434,7 @@
         <v>346045</v>
       </c>
     </row>
-    <row r="798" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A798" s="13">
         <v>2021</v>
       </c>
@@ -19447,7 +19457,7 @@
         <v>424165</v>
       </c>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A799" s="16">
         <v>2021</v>
       </c>
@@ -19470,7 +19480,7 @@
         <v>426351</v>
       </c>
     </row>
-    <row r="800" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A800" s="13">
         <v>2021</v>
       </c>
@@ -19493,7 +19503,7 @@
         <v>473392</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A801" s="16">
         <v>2021</v>
       </c>
@@ -19516,7 +19526,7 @@
         <v>677084</v>
       </c>
     </row>
-    <row r="802" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A802" s="13">
         <v>2021</v>
       </c>
@@ -19539,7 +19549,7 @@
         <v>662816</v>
       </c>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A803" s="16">
         <v>2021</v>
       </c>
@@ -19562,7 +19572,7 @@
         <v>121295</v>
       </c>
     </row>
-    <row r="804" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A804" s="13">
         <v>2021</v>
       </c>
@@ -19585,7 +19595,7 @@
         <v>29991</v>
       </c>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A805" s="16">
         <v>2021</v>
       </c>
@@ -19608,7 +19618,7 @@
         <v>70313</v>
       </c>
     </row>
-    <row r="806" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A806" s="13">
         <v>2021</v>
       </c>
@@ -19631,7 +19641,7 @@
         <v>276164</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A807" s="16">
         <v>2021</v>
       </c>
@@ -19654,7 +19664,7 @@
         <v>644268</v>
       </c>
     </row>
-    <row r="808" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A808" s="13">
         <v>2021</v>
       </c>
@@ -19677,7 +19687,7 @@
         <v>278937</v>
       </c>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A809" s="16">
         <v>2021</v>
       </c>
@@ -19700,7 +19710,7 @@
         <v>328871</v>
       </c>
     </row>
-    <row r="810" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A810" s="13">
         <v>2021</v>
       </c>
@@ -19723,7 +19733,7 @@
         <v>651501</v>
       </c>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A811" s="16">
         <v>2021</v>
       </c>
@@ -19746,7 +19756,7 @@
         <v>1702011</v>
       </c>
     </row>
-    <row r="812" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A812" s="13">
         <v>2021</v>
       </c>
@@ -19769,7 +19779,7 @@
         <v>52304</v>
       </c>
     </row>
-    <row r="813" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A813" s="16">
         <v>2021</v>
       </c>
@@ -19792,7 +19802,7 @@
         <v>29547</v>
       </c>
     </row>
-    <row r="814" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A814" s="13">
         <v>2021</v>
       </c>
@@ -19815,7 +19825,7 @@
         <v>30851</v>
       </c>
     </row>
-    <row r="815" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A815" s="16">
         <v>2021</v>
       </c>
@@ -19838,7 +19848,7 @@
         <v>27551</v>
       </c>
     </row>
-    <row r="816" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A816" s="13">
         <v>2021</v>
       </c>
@@ -19861,7 +19871,7 @@
         <v>21381</v>
       </c>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A817" s="16">
         <v>2021</v>
       </c>
@@ -19884,7 +19894,7 @@
         <v>37907</v>
       </c>
     </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A818" s="13">
         <v>2021</v>
       </c>
@@ -19907,7 +19917,7 @@
         <v>30873</v>
       </c>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A819" s="16">
         <v>2021</v>
       </c>
@@ -19930,7 +19940,7 @@
         <v>31660</v>
       </c>
     </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A820" s="13">
         <v>2021</v>
       </c>
@@ -19953,7 +19963,7 @@
         <v>19210</v>
       </c>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A821" s="16">
         <v>2021</v>
       </c>
@@ -19976,7 +19986,7 @@
         <v>72915</v>
       </c>
     </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A822" s="13">
         <v>2021</v>
       </c>
@@ -19999,7 +20009,7 @@
         <v>31887</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A823" s="16">
         <v>2021</v>
       </c>
@@ -20022,7 +20032,7 @@
         <v>37495</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A824" s="13">
         <v>2021</v>
       </c>
@@ -20045,7 +20055,7 @@
         <v>30362</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A825" s="16">
         <v>2021</v>
       </c>
@@ -20068,7 +20078,7 @@
         <v>29387</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A826" s="13">
         <v>2021</v>
       </c>
@@ -20091,7 +20101,7 @@
         <v>34913</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A827" s="16">
         <v>2021</v>
       </c>
@@ -20114,7 +20124,7 @@
         <v>35226</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A828" s="13">
         <v>2021</v>
       </c>
@@ -20137,7 +20147,7 @@
         <v>32245</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A829" s="16">
         <v>2021</v>
       </c>
@@ -20160,7 +20170,7 @@
         <v>20088</v>
       </c>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A830" s="13">
         <v>2021</v>
       </c>
@@ -20183,7 +20193,7 @@
         <v>218670</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A831" s="16">
         <v>2021</v>
       </c>
@@ -20206,7 +20216,7 @@
         <v>118682</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A832" s="13">
         <v>2021</v>
       </c>
@@ -20229,7 +20239,7 @@
         <v>97724</v>
       </c>
     </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A833" s="16">
         <v>2021</v>
       </c>
@@ -20252,7 +20262,7 @@
         <v>84120</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A834" s="13">
         <v>2021</v>
       </c>
@@ -20275,7 +20285,7 @@
         <v>88905</v>
       </c>
     </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A835" s="16">
         <v>2021</v>
       </c>
@@ -20298,7 +20308,7 @@
         <v>139923</v>
       </c>
     </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A836" s="13">
         <v>2021</v>
       </c>
@@ -20321,7 +20331,7 @@
         <v>92321</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A837" s="16">
         <v>2021</v>
       </c>
@@ -20344,7 +20354,7 @@
         <v>111192</v>
       </c>
     </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A838" s="13">
         <v>2021</v>
       </c>
@@ -20367,7 +20377,7 @@
         <v>62378</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A839" s="16">
         <v>2021</v>
       </c>
@@ -20390,7 +20400,7 @@
         <v>805686</v>
       </c>
     </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A840" s="13">
         <v>2021</v>
       </c>
@@ -20413,7 +20423,7 @@
         <v>245859</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A841" s="16">
         <v>2021</v>
       </c>
@@ -20436,7 +20446,7 @@
         <v>246287</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A842" s="13">
         <v>2021</v>
       </c>
@@ -20459,7 +20469,7 @@
         <v>216804</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A843" s="16">
         <v>2021</v>
       </c>
@@ -20482,7 +20492,7 @@
         <v>204319</v>
       </c>
     </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A844" s="13">
         <v>2021</v>
       </c>
@@ -20505,7 +20515,7 @@
         <v>280151</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A845" s="16">
         <v>2021</v>
       </c>
@@ -20528,7 +20538,7 @@
         <v>236904</v>
       </c>
     </row>
-    <row r="846" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A846" s="13">
         <v>2021</v>
       </c>
@@ -20551,7 +20561,7 @@
         <v>221479</v>
       </c>
     </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A847" s="16">
         <v>2021</v>
       </c>
@@ -20574,7 +20584,7 @@
         <v>142616</v>
       </c>
     </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A848" s="13">
         <v>2021</v>
       </c>
@@ -20597,7 +20607,7 @@
         <v>14238819</v>
       </c>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A849" s="16">
         <v>2021</v>
       </c>
@@ -20620,7 +20630,7 @@
         <v>2743033</v>
       </c>
     </row>
-    <row r="850" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A850" s="13">
         <v>2021</v>
       </c>
@@ -20643,7 +20653,7 @@
         <v>2483017</v>
       </c>
     </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A851" s="16">
         <v>2021</v>
       </c>
@@ -20666,7 +20676,7 @@
         <v>3749657</v>
       </c>
     </row>
-    <row r="852" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A852" s="13">
         <v>2021</v>
       </c>
@@ -20689,7 +20699,7 @@
         <v>5471639</v>
       </c>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A853" s="16">
         <v>2021</v>
       </c>
@@ -20712,7 +20722,7 @@
         <v>7146157</v>
       </c>
     </row>
-    <row r="854" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A854" s="13">
         <v>2021</v>
       </c>
@@ -20735,7 +20745,7 @@
         <v>3142761</v>
       </c>
     </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A855" s="16">
         <v>2021</v>
       </c>
@@ -20758,7 +20768,7 @@
         <v>4134036</v>
       </c>
     </row>
-    <row r="856" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A856" s="13">
         <v>2021</v>
       </c>
@@ -20781,7 +20791,7 @@
         <v>6486431</v>
       </c>
     </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A857" s="16">
         <v>2021</v>
       </c>
@@ -20804,7 +20814,7 @@
         <v>431186</v>
       </c>
     </row>
-    <row r="858" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A858" s="13">
         <v>2021</v>
       </c>
@@ -20827,7 +20837,7 @@
         <v>1339003</v>
       </c>
     </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A859" s="16">
         <v>2021</v>
       </c>
@@ -20850,7 +20860,7 @@
         <v>818473</v>
       </c>
     </row>
-    <row r="860" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A860" s="13">
         <v>2021</v>
       </c>
@@ -20873,7 +20883,7 @@
         <v>763677</v>
       </c>
     </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A861" s="16">
         <v>2021</v>
       </c>
@@ -20896,7 +20906,7 @@
         <v>815605</v>
       </c>
     </row>
-    <row r="862" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A862" s="13">
         <v>2021</v>
       </c>
@@ -20919,7 +20929,7 @@
         <v>1195860</v>
       </c>
     </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A863" s="16">
         <v>2021</v>
       </c>
@@ -20942,7 +20952,7 @@
         <v>900229</v>
       </c>
     </row>
-    <row r="864" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A864" s="13">
         <v>2021</v>
       </c>
@@ -20965,7 +20975,7 @@
         <v>1368183</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A865" s="16">
         <v>2021</v>
       </c>
@@ -20988,7 +20998,7 @@
         <v>925155</v>
       </c>
     </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A866" s="13">
         <v>2021</v>
       </c>
@@ -21011,7 +21021,7 @@
         <v>460795</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A867" s="16">
         <v>2021</v>
       </c>
@@ -21034,7 +21044,7 @@
         <v>252360</v>
       </c>
     </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A868" s="13">
         <v>2021</v>
       </c>
@@ -21057,7 +21067,7 @@
         <v>230449</v>
       </c>
     </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A869" s="16">
         <v>2021</v>
       </c>
@@ -21080,7 +21090,7 @@
         <v>188702</v>
       </c>
     </row>
-    <row r="870" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A870" s="13">
         <v>2021</v>
       </c>
@@ -21103,7 +21113,7 @@
         <v>187694</v>
       </c>
     </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A871" s="16">
         <v>2021</v>
       </c>
@@ -21126,7 +21136,7 @@
         <v>167670</v>
       </c>
     </row>
-    <row r="872" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A872" s="13">
         <v>2021</v>
       </c>
@@ -21149,7 +21159,7 @@
         <v>126255</v>
       </c>
     </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A873" s="16">
         <v>2021</v>
       </c>
@@ -21172,7 +21182,7 @@
         <v>344761</v>
       </c>
     </row>
-    <row r="874" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A874" s="13">
         <v>2021</v>
       </c>
@@ -21195,7 +21205,7 @@
         <v>436617</v>
       </c>
     </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A875" s="16">
         <v>2021</v>
       </c>
@@ -21218,7 +21228,7 @@
         <v>1180071</v>
       </c>
     </row>
-    <row r="876" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A876" s="13">
         <v>2021</v>
       </c>
@@ -21241,7 +21251,7 @@
         <v>458643</v>
       </c>
     </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A877" s="16">
         <v>2021</v>
       </c>
@@ -21264,7 +21274,7 @@
         <v>687897</v>
       </c>
     </row>
-    <row r="878" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A878" s="13">
         <v>2021</v>
       </c>
@@ -21287,7 +21297,7 @@
         <v>497711</v>
       </c>
     </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A879" s="16">
         <v>2021</v>
       </c>
@@ -21310,7 +21320,7 @@
         <v>277839</v>
       </c>
     </row>
-    <row r="880" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A880" s="13">
         <v>2021</v>
       </c>
@@ -21333,7 +21343,7 @@
         <v>237597</v>
       </c>
     </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A881" s="16">
         <v>2021</v>
       </c>
@@ -21356,7 +21366,7 @@
         <v>190608</v>
       </c>
     </row>
-    <row r="882" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A882" s="13">
         <v>2021</v>
       </c>
@@ -21379,7 +21389,7 @@
         <v>294322</v>
       </c>
     </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A883" s="16">
         <v>2021</v>
       </c>
@@ -21402,7 +21412,7 @@
         <v>295440</v>
       </c>
     </row>
-    <row r="884" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A884" s="13">
         <v>2021</v>
       </c>
@@ -21425,7 +21435,7 @@
         <v>5842025</v>
       </c>
     </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A885" s="16">
         <v>2021</v>
       </c>
@@ -21448,7 +21458,7 @@
         <v>2323444</v>
       </c>
     </row>
-    <row r="886" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A886" s="13">
         <v>2021</v>
       </c>
@@ -21471,7 +21481,7 @@
         <v>2433274</v>
       </c>
     </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A887" s="16">
         <v>2021</v>
       </c>
@@ -21494,7 +21504,7 @@
         <v>3000053</v>
       </c>
     </row>
-    <row r="888" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A888" s="13">
         <v>2021</v>
       </c>
@@ -21517,7 +21527,7 @@
         <v>1149672</v>
       </c>
     </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A889" s="16">
         <v>2021</v>
       </c>
@@ -21540,7 +21550,7 @@
         <v>1057472</v>
       </c>
     </row>
-    <row r="890" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A890" s="13">
         <v>2021</v>
       </c>
@@ -21563,7 +21573,7 @@
         <v>835208</v>
       </c>
     </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A891" s="16">
         <v>2021</v>
       </c>
@@ -21586,7 +21596,7 @@
         <v>509616</v>
       </c>
     </row>
-    <row r="892" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A892" s="13">
         <v>2021</v>
       </c>
@@ -21609,7 +21619,7 @@
         <v>474682</v>
       </c>
     </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A893" s="16">
         <v>2021</v>
       </c>
@@ -21632,7 +21642,7 @@
         <v>15339259</v>
       </c>
     </row>
-    <row r="894" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A894" s="13">
         <v>2021</v>
       </c>
@@ -21655,7 +21665,7 @@
         <v>1764404</v>
       </c>
     </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A895" s="16">
         <v>2021</v>
       </c>
@@ -21678,7 +21688,7 @@
         <v>2920084</v>
       </c>
     </row>
-    <row r="896" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A896" s="13">
         <v>2021</v>
       </c>
@@ -21701,7 +21711,7 @@
         <v>4843996</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A897" s="16">
         <v>2021</v>
       </c>
@@ -21724,7 +21734,7 @@
         <v>5451357</v>
       </c>
     </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A898" s="13">
         <v>2021</v>
       </c>
@@ -21747,7 +21757,7 @@
         <v>3794303</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A899" s="16">
         <v>2021</v>
       </c>
@@ -21770,7 +21780,7 @@
         <v>3135980</v>
       </c>
     </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A900" s="13">
         <v>2021</v>
       </c>
@@ -21793,7 +21803,7 @@
         <v>4900876</v>
       </c>
     </row>
-    <row r="901" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A901" s="16">
         <v>2021</v>
       </c>
@@ -21814,6 +21824,32 @@
       </c>
       <c r="G901" s="18">
         <v>11165813</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157CA672-AA0C-4B46-BD04-3BA0945073F5}">
+  <dimension ref="F4:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="4" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>34234234</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -21831,6 +21867,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a6b62d7a-dd09-46e4-b53c-18efd117aad1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="af56a8d8-8409-452c-af23-431516952e37" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010056771D67E9AD9A479B2DB2075AB77E1A" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="41a1a0edc924dd6ac7ec2eadc95eb735">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a6b62d7a-dd09-46e4-b53c-18efd117aad1" xmlns:ns3="af56a8d8-8409-452c-af23-431516952e37" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60f56773215438a58a33db1de9fa6f09" ns2:_="" ns3:_="">
     <xsd:import namespace="a6b62d7a-dd09-46e4-b53c-18efd117aad1"/>
@@ -22071,17 +22118,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a6b62d7a-dd09-46e4-b53c-18efd117aad1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="af56a8d8-8409-452c-af23-431516952e37" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE4545FF-2F1A-440E-95B5-4DF57A426DD4}">
   <ds:schemaRefs>
@@ -22091,6 +22127,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68F3102A-B332-4634-8FDA-ADB34DC38FB0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a6b62d7a-dd09-46e4-b53c-18efd117aad1"/>
+    <ds:schemaRef ds:uri="af56a8d8-8409-452c-af23-431516952e37"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45CFAE8B-BAA0-4D67-845E-09924AAEECE3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22107,15 +22154,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68F3102A-B332-4634-8FDA-ADB34DC38FB0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a6b62d7a-dd09-46e4-b53c-18efd117aad1"/>
-    <ds:schemaRef ds:uri="af56a8d8-8409-452c-af23-431516952e37"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>